--- a/CS-Testing/06-Requirements-Review/SOW1-SOW2_Review_Log.xlsx
+++ b/CS-Testing/06-Requirements-Review/SOW1-SOW2_Review_Log.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key decisions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review (detailed)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key decisions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Review'!$A$1:$S$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Review'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review (detailed)'!$A$1:$S$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +38,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -78,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -88,6 +95,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,6 +464,1793 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement text</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SIQ</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impact and proposal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Testability Finding</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Finding</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Structure Finding</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Traceability Finding</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>How to test (pseudo-code)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Decision note</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="66" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>MVC-119709</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Verify frame tag</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>The system shall verify the integrity and authenticity of each video frame by comparing the calculated AES-CMAC tag with the 128-bit CMAC tag received in the frame footer.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>• Frames 1-17 carry no tag: drop, accept or show?
+• Which rows does the CMAC cover?</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>• Text says 'each frame'; imager tags only frames 18+ and only selected rows.
+• Reword: 'each frame that carries a tag, over the selected rows'. Add a requirement for untagged frames.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>• Comparison is internal; same observable as 119710. Use the log event or a drop counter.
+• SIM needed: tester must know the session key.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>• Unselected rows and statistics are not authenticated.
+• No latency limit for holding a frame until verified.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>• Merge with 119710, or split compare (119709) from reaction (119710).
+• TCR 106582 copies the text: add algorithm and input.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106582 (ok).
+• Upstream MVC-106231 is too generic.
+• SRS 108112/108117/108122: link missing.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SIM: correct tag -&gt; frame accepted (RTP seen)
+SIM: flip 1 tag bit / truncate / wrong key / zero tag -&gt; rejected
+UART log: 'CMAC failed'</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>MVC-107641</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>RSASSA-PSS with SHA-256</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>The system shall use RSASSA-PSS with SHA-256 to verify the Imager's digital signature.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>• PSS salt length and MGF?
+• Does KID select the scheme (SRS 108135)?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>• If only PSS/SHA-256 exists, drop the KID selection in the SRS; otherwise list accepted KIDs.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>• Partly inspection.
+• PKCS#1 v1.5 or another hash must fail; salt cases need the salt defined.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>• Salt length, MGF and exponent are not stated.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>• Property of the 107642 verification: merge or keep as technical detail.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>• MVC-106563 does not link back: add the link.
+• SRS 108120, 108135, 108136.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Review: verify call = RSASSA-PSS + SHA-256
+PyRef: PSS/SHA-256 -&gt; accepted
+PKCS#1 v1.5, SHA-1, SHA-384 -&gt; rejected</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="66" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103042</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CSPRNG and TRNG</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>The system shall use a CSPRNG compliant with NIST SP 800-90A and seeded by a hardware TRNG to generate the 256-bit session key.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>• Which DRBG and TRNG interface?
+• Evidence for SP 800-90A and TRNG quality (Ambarella)?</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>• Conformity is a design property: change the method to Review.
+• Keep a test for the failure behaviour.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>• Black-box shows only uniqueness.
+• Inject a TRNG error with Lauterbach.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>• SP 800-90A covers the DRBG, not the entropy source (800-90B).
+• No reseed rule.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>• Same TRNG as debug requirement MVC-103050.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106560.
+• SRS 108106, 108109, 23.1.1.2.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Review: DRBG type and TRNG seed call; collect evidence
+Lauterbach: force TRNG error -&gt; no key block (Saleae)
+Collect 1000 SSKs via SIM -&gt; no repeats</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103034</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Transmit encrypted SSK</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>The system shall transmit the 2048bit Encrypted Session Key and row information to the Imager for secure session establishment.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>• How does SOW2 know the imager accepted the key block?</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>• 'Session established' is undefined; 119708, 103046, 103044 depend on it.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>• Capture the write with Saleae; layout from the Samsung note.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>• I2C CRC is ON (Volvo spec); a 256-byte block may need several writes: partial writes undefined.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106578.
+• SRS 108146, 108145.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Saleae: after auth OK, write to imager key register = encrypted block, right length
+Order: auth read -&gt; verify -&gt; key write
+SIM acks -&gt; SESSION_ACTIVE; silent -&gt; not active</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103051</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Terminate authentication</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>The system shall terminate the Imager authentication process if authentication is not successfully completed within the configured maximum number of retry attempts</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>• After termination: no video, retry later, or safe state?
+• When is the next attempt allowed?</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>• A cybersecurity failure can switch off the camera image.
+• Define the reaction with FuSa.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>• End state is observable (state, bus, stream).
+• 'No retry forever' needs a defined observation time.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>• Concept says 'configured maximum', technical says a fixed three.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>• See 103053.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106569.
+• SRS 108124 is similar.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SIM never gives valid data; reset
+Saleae: no auth request or key write for 60 s
+Lauterbach: state UNAUTHENTICATED; valid-tag frames rejected
+Power cycle -&gt; new attempt</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103044</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Terminate session establishment</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>The system shall terminate secure session establishment if a secure session is not successfully established after three retry attempts.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>• Reaction after termination: no video, new auth, or safe state?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>• Define the next step and whether retries restart after a new authentication.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>• End state is observable: no session, no more writes, key unused.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>• The failed attempt's SSK must be erased (SRS 108149): check the buffer.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106581.
+• SRS 108149, 108158.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SIM never acks the key block
+Saleae: no key writes for 60 s after last retry
+Lauterbach: state INACTIVE, key buffer zero
+Tagged frames rejected; reset -&gt; new attempt</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103063</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Root key in OTP</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>The system shall store the trusted 2048bit Samsung Root Public Key in OTP memory.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>• Which OTP zone, and who programs it and when?</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>• Add 'prevent modification, replacement, deletion' (only in the verification text today).
+• Name the zone.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>• OTP is write-once: the overwrite test destroys a sample.
+• Test samples need a test root key.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>• Concept says OTP, SRS 108143 says 'protected non-volatile storage'.
+• Check free OTP size.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>• Technical requirement copies the concept text.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106562.
+• SRS 108143, 108142, 108144.
+• Secure-boot key (SRS 23.4) is a separate root.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Lauterbach: read OTP zone; SHA-256(key) = Samsung fingerprint
+Try to write the zone -&gt; rejected; power cycle -&gt; unchanged
+SIM signs with test root -&gt; auth passes; other key -&gt; fails</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103053</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Retry authentication</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>The system shall retry the Imager authentication process up to three times if the expected authentication data is failed to be received.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>• 3 retries (4 requests) or 3 attempts (3 requests)?
+• Timeout per attempt?</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>• Request count cannot be tested without one number.
+• Define N attempts in total and timeout T.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>• Count requests with Saleae; SIM withholds the answer.
+• Timing untestable until T is defined.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>• 'Not received' vs invalid data: is a bad signature retried?</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>• Retry rule is split over 103053 and 103051 with different wording.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106566.
+• SRS 108124, 108126.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SIM: no answer to the auth read; reset
+Saleae: count auth requests until SOW2 stops = N
+SIM answers on request 2 -&gt; authentication continues</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103046</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Retry session establishment</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>The system shall retry secure session establishment up to three times if the expected response is failed to be received.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>• What is the 'expected response', and the timeout per try?
+• Same block or new SSK on retry?</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>• Define the response, the timeout and what is resent.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>• Count with Saleae; SIM withholds the response.
+• Blocked until the response is defined.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106567.
+• SRS 108149.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SIM accepts auth, ignores the key block
+Saleae: key writes = 1 + 3 (as decided)
+SIM answers on the 2nd -&gt; session established</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103036</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>New session after triggers</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>The system shall require establishment of a new secure session, including full SOW1 authentication and generation of a new session key (SSK), after session expiry, system reset, system restart, session termination, or detection of a security failure.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>• Session lifetime?
+• Which events are a 'security failure'?
+• Reset vs restart?</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>• 2 of 5 triggers are untestable; conflicts with 'reject one frame and continue'.
+• Define lifetime and failure threshold; merge reset and restart.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>• Each trigger is testable alone; SIM replays the old key afterwards.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>• Video interruption during renegotiation is not limited.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>• Five triggers in one requirement: test each separately.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106573.
+• SRS 108156, 108158, 108151.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>For each trigger (expiry, reset, restart, termination, failure): establish session, fire trigger
+Saleae: new auth + new key block; SIM: SSK_new != SSK_old
+Frames with SSK_old -&gt; rejected</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>MVC-113703</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Freshness window</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>The system shall reject duplicated, stale, or out-of-order SOW1 video frames based on a 3-frame freshness window and shall accept a frame only when its frame counter satisfies LastAcceptedCounter &lt; ReceivedCounter ≤ LastAcceptedCounter + 3.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• Counter wrap and first-frame value after a new session?</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>• More than 3 lost frames blocks every later valid frame until a new session.
+• Define a recovery.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>• Boundaries are easy (=, &lt;, +1 to +4).
+• Wrap and first frame untestable until defined.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>• Update LastAcceptedCounter only after the CMAC passes: state the order.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-113727.
+• SRS 108099, 108104, 108102.
+• Recovery is in no requirement.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SIM (valid CMAC): n; n again -&gt; reject; n-1 -&gt; reject; n+1, n+3 -&gt; accept; n+4 -&gt; reject
+Forged high counter + wrong tag -&gt; rejected, LastAccepted unchanged (Lauterbach)
+Skip 5 frames -&gt; observe recovery</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>MVC-119710</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Reject frame on failure</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>The system shall reject any received SOW1 video frame if AES-CMAC verification fails.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>• What does 'reject' do: drop, repeat previous frame, flag?</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>• Reaction undefined on a display camera.
+• Define: drop, count, log, continue (SRS 108105).</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>• Same observable as 119709: define log or counter.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>• No threshold for repeated bad frames.
+• Random corruption and forgery get the same reaction?</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>• Overlaps 119709 and SRS 108116.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106564 (ok).
+• SRS 108116, 108108, 108105.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SIM: 10 good, 1 bad tag, 10 good
+Wireshark: bad frame missing from RTP
+Lauterbach: drop counter = 1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>MVC-119714</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>No commands before authentication</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>The system shall not transmit SOW1 control commands before successful SOW1 device authentication.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>• Which commands are 'control commands'?
+• Which I2C writes are allowed before authentication?</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>• Read literally, it forbids the writes needed to start the camera.
+• Use 'protected' and list the commands.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>• Saleae lists all writes; the pass criterion needs the command list.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>• Volvo spec has no protected command channel.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>• Concept says 'control commands', technical says 'protected'.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-109119.
+• SRS 108169.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Reset, auth blocked; trigger a protected command
+Saleae: only allowed pre-auth writes, no protected command
+After auth + session -&gt; command is sent</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>MVC-113706</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Do not expose SSK</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>The system shall not expose the active session key through any accessible interface during the active secure session.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>• 'Any accessible interface' needs a list: UART, JTAG, logs, SOME/IP/DTLS diagnostics, dumps, I2C, flash.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>• Negative test: needs the interface list and the SSK (from SIM).</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>• SSK is in DRAM; authorised debug can read it.
+• Exclude the key region or accept an exception.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>• Technical requirement copies the text; SRS has 4 related requirements.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106571.
+• SRS 108164, 108163, 108154, 108157; debug and DRAM requirements.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SIM: get SSK; JTAG locked -&gt; Lauterbach denied
+Search I2C, Ethernet, UART captures for SSK bytes -&gt; none
+Trigger failures, read logs -&gt; no key
+Unlocked debug: read DRAM key region -&gt; record</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>MVC-119708</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>No trust before session</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>The system shall not accept SOW1 secured video stream data as trusted before successful SOW1 device authentication and secure session establishment.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>• What happens to 'untrusted' video: dropped or passed with a flag? (safety decision)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>• Two very different implementations are possible.
+• Define the reaction and who evaluates it.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>• Observable only on the outgoing RTP stream or a status signal.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>• 'Session established' is not defined (see 103034).</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-109120.
+• SRS 108138.
+• Reaction is in no requirement.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Reset; SIM silent on authentication
+SIM sends frames -&gt; Wireshark: no trusted video
+Repeat after auth failure and after session end; after auth + session -&gt; video flows</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>MVC-113702</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Command counter</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>The system shall include a monotonically increasing Counter in each SOW1 control command transmitted.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>• Counter width, start value, max behaviour?
+• Does the imager check it?</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>• 'Monotonic' allows equal values: use 'strictly increasing, no reuse in a session' (SRS 108161).
+• State the wrap rule.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>• Read counters with Saleae.
+• Max case needs a preset hook.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>• Replay protection exists only if the imager rejects old counters.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>• See 113701.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-109121.
+• SRS 108159, 108161.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Send 100 commands; Saleae: strictly increasing
+Reset -&gt; counter restarts as defined
+Lauterbach: preset near max -&gt; new session before wrap
+If imager checks: replay old command -&gt; rejected</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103057</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Generate 256-bit SSK</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>The system shall generate a 256-bit cryptographically random session key (SSK) following successful Imager authentication.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>• 'New key every session' is only in the verification text: add it (SRS 108110).</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>• SSK is visible only through the SIM.
+• Randomness cannot be proven, only repeats.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>• Overlaps 103042 (how) and 103036 (new each session).
+• Keep length + new-each-session here.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106568.
+• SRS 108107, 108110.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Loop 1000: reset, authenticate, SIM decrypts key block, store SSK
+Check: 32 bytes, no duplicates
+Auth failure -&gt; no key block on I2C</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103031</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Extract frame counter</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>The system shall extract the video frame counter from the embedded header data of each received SOW1 video frame and use the counter value for freshness validation.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>• Counter width, start value, wrap, reset per stream?</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>• Window rule cannot be checked at wrap without the width.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>• Read the counter with Lauterbach.
+• SIM sends boundary values.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>• Counter is protected only if the header row is inside the CMAC rows (start row 0).</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>• 'Use for freshness' duplicates 113703 / MVC-106575: keep extraction only.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-113726 and MVC-106575.
+• SRS 108099.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SIM: counters 1..N
+Lauterbach: extracted counter = sent value
+SIM: counter at max, then 0 -&gt; defined wrap; missing header -&gt; rejected</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>MVC-113705</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Extract tag from footer</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>The system shall extract the received 128-bit AES-CMAC authentication tag from the embedded footer of each received SOW1 video frame.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>• Footer position, length, byte order? (Samsung note missing)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>• Layout needed to implement and test.
+• Add the layout reference to the technical requirement.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>• Internal step: read the buffer with Lauterbach or infer from acceptance.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>• Footer is absent in frames 1-17.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>• Implementation step of 119709: keep at technical level or merge.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106572.
+• SRS 108140, 108129, 108134, 108132.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SIM: frame with known tag T
+Lauterbach: extracted tag = T (10 different tags)
+SIM: missing or short footer -&gt; rejected, no crash</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103055</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Encrypt SSK and Row_info</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>The system shall encrypt the session key and selected row information using the 2048-bit device public key with RSAES-OAEP and SHA-256. (Note: row information format is defined by Samsung, chapter 5 Key sharing of the S5K3B6SA cybersecurity application note.)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>• Message layout (SSK, Row_info_00/01), OAEP label, MGF1 hash? (Samsung note missing)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>• Layout is needed by implementation and test: put it in the technical requirement.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>• OAEP is randomised: compare plaintexts only.
+• Known SSK needs a test hook.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>• RSA-2048 OAEP/SHA-256 holds max 190 bytes: 32-byte SSK + Row_info fits.
+• Row rules depend on the output mode.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>• 4 technical requirements, 3 about row selection: give row selection its own concept requirement.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106580, 106576, 108741, 106574.
+• SRS 108153, 108145, 108165, 108166.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SIM: decrypt key block (OAEP, SHA-256) -&gt; SSK + Row_info
+Lauterbach: Row_info used = decrypted
+Wrong private key -&gt; fails; no SSK in plaintext on I2C
+Bad row settings -&gt; refused</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103033</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Calculate frame CMAC</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>The system shall calculate a 128-bit AES-CMAC tag over the selected rows of each video frame using the active 256-bit session key.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>• Exact CMAC input bytes: pixel data only, or line headers too?
+• Row numbering base?</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>• Two implementations could produce different tags.
+• Add exact input and a Samsung test vector.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>• Reference calculation needs the SSK and exact input: SIM only.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>• AES-256 CMAC, full 128-bit tag: state 'not truncated'.
+• No host-side speed requirement.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>• Row selection is defined in 4 other requirements: give it its own concept requirement.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106583.
+• SRS 108122, 108121, 108118.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>TE-1190: capture frame rows
+PyRef: tag = AES256-CMAC(SSK, selected rows)
+SIM: send -&gt; accepted; change 1 byte in a selected row -&gt; rejected; in an unselected row -&gt; accepted</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>MVC-113701</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>CMAC over each command</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>The system shall calculate a 128-bit AES-CMAC over each SOW1 control command using the established 256-bit session key.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>• Does the imager verify command tags at all?
+• Command format and CMAC input?</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>• If the imager does not check, the tag adds nothing: confirm first.
+• Then fix the input (command + counter, SRS 108159).</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>• Tag checkable with PyRef.
+• Imager rejection untestable if it does not check.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>• Concept: 'each command'. SRS: 'only when supported by SOW1'. Conflict.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>• 113701, 119707, 113702 are steps of one function: merge into one 'protected command format'.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-108740.
+• SRS 108160, 108159.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Trigger a protected command
+Saleae: parse cmd | counter | tag
+PyRef: AES256-CMAC(SSK, cmd||counter) = tag
+If imager checks: wrong tag -&gt; rejected</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="78" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>MVC-107642</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Authenticate imager</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>The system shall authenticate the Imager by verifying the digital signature received from the Imager over the I2C interface using the provisioned Samsung Root Public Key.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>• Define Device_n, KID, Sig_device and the exact signed message (Volvo spec: key + Device ID).</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>• Signed message must be defined byte for byte, or SOW2 and test disagree.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>• Needs signatures from a test root key.
+• Negative cases need the SIM.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>• Signature is static (no challenge): a copied record passes this step.
+• Only the CMAC (frame 18+) proves the private key.
+• Concept fixes the scheme, SRS lets KID choose.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>• Three technical requirements verify it: keep tests separate per topic.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106561/106565/106563.
+• SRS 108133, 108131, 108126, 108124, 108113, 108111.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SIM serves genuine data -&gt; Saleae: key block follows
+Flip 1 bit in Device_n / KID / Sig -&gt; rejected, no key sent
+Replay genuine data without the private key -&gt; auth passes, frames rejected</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>MVC-119707</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Append tag to command</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>The system shall append the calculated 128-bit AES-CMAC tag to each SOW1 control command before transmission.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>• Field order and size in the I2C write?
+• Where does the I2C CRC go?</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>• Define the layout in the technical requirement, with an example.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>• Easy with Saleae once the layout is defined.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>• If CMAC generation fails, no command may be sent (SRS 108160): add it.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>• See 113701.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106570.
+• SRS 108160.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Saleae: write = [cmd][counter][16-byte tag] in the defined order
+Lauterbach: force CMAC failure -&gt; nothing sent
+Repeat for 3 commands</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>MVC-103040</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Extract device public key</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Following successful authentication, The system shall extract 2048-bit device public key from the Imager's authentication data.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>• Key format: modulus only? Fixed exponent?</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>• Add sanity checks (2048 bit, odd modulus, exponent) before use.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>• Internal: check indirectly. SIM decrypts the key block with its private key.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>• Key is covered by the signature only if Device_n is the modulus.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>• Linked to MVC-106577.
+• SRS 108153.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SIM: decrypt SOW2's key block with K1 private -&gt; success
+SIM key of 1024 or 4096 bits, valid signature -&gt; rejected
+Truncated or zero key -&gt; rejected</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N26"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L2:L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,AGREED,CHANGE REQUESTED,REJECTED,CLARIFY WITH EXTERNAL"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -669,9 +2466,9 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
     </row>
     <row r="3" ht="240" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -679,17 +2476,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MVC-119710</t>
+          <t>MVC-107641</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Reject frame on failure</t>
+          <t>RSASSA-PSS with SHA-256</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2.2.1.1.4-5</t>
+          <t>2.2.1.1.2-2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -704,47 +2501,52 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>The system shall reject any received SOW1 video frame if AES-CMAC verification fails.</t>
+          <t>The system shall use RSASSA-PSS with SHA-256 to verify the Imager's digital signature.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>MVC-106564. Test: CS-SOW1-022.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>MVC-106563 (no link back in Polarion). Test: CS-SOW1-004.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>PSS parameters: salt length, mask generation function (MGF1 with SHA-256?). And the SRS lets KID choose scheme and hash (MVC-108135, 108120). Is PSS with SHA-256 the only supported one?</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>"Reject" is not defined: dropped, replaced by the previous frame, or shown with a flag? This is a camera that drives a display, so a defined reaction matters. Proposal: state the reaction (drop the frame, count it, log it, keep processing the next frames, which SRS MVC-108105 already says) and when repeated failures start a new session (see 103036).</t>
+          <t>if only one scheme exists, tell the SRS to drop the selection by KID. If KID selects among several, this requirement must say which values of KID are accepted.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>the observable is the same as 119709. Define it once: dropped frame counter and log event. The VC step "does not cause the same invalid frame to be re-submitted" needs a defined internal buffer to look at.</t>
+          <t>partly an inspection (the technical verification criteria say "implementation inspection"). The black-box part: signatures made with PKCS#1 v1.5, other hashes or other salt lengths must fail. The salt-length case cannot be written until the salt is defined.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>no limit on how many bad frames are tolerated before the stream is treated as an attack. A single corrupted frame from EMI on the cable would also fail the CMAC (the link has CRC, but the check here is separate). Question: do random corruption and a forged frame get the same reaction?</t>
+          <t>salt length, MGF and exponent are not stated.</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>overlaps 119709 (see entry 1). Overlaps SRS MVC-108116.</t>
+          <t>it is a property of the verification in 107642, not a stand-alone behaviour. Proposal: merge into 107642 or keep as a technical detail.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>MVC-106564 (link both ways). SRS MVC-108116, 108108, 108105. Same upstream as 119709.</t>
+          <t>the technical requirement MVC-106563 does not link to it (only to 107642). Add the link. SRS MVC-108120, 108135, 108136.</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>SIM: send 10 good frames, 1 frame with wrong tag, 10 good frames
-Wireshark: RTP shows 20 frames, the bad one missing        -&gt; expect: bad frame not forwarded
-UART log: 1 "CMAC failed" entry                            -&gt; expect: logged
-Lauterbach: read dropped-frame counter                     -&gt; expect: 1
-SIM: send 1000 frames, each with a wrong tag                -&gt; expect: defined reaction (new session or stay up) once decided
+          <t>Code review: verify call = RSASSA-PSS + SHA-256 (CS-SOW1-004 step 1)
+PyRef: sign (Device_n||KID) with test root key:
+   PSS+SHA-256   -&gt; SIM serves -&gt; expect: accepted
+   PKCS#1 v1.5   -&gt; expect: rejected
+   PSS+SHA-1 or SHA-384 -&gt; expect: rejected
+   PSS+SHA-256, other salt length -&gt; expect: as defined (once the salt is fixed)
 Decision: OPEN
 ---</t>
         </is>
@@ -754,9 +2556,9 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
     </row>
     <row r="4" ht="240" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -764,17 +2566,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MVC-113705</t>
+          <t>MVC-103042</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Extract tag from footer</t>
+          <t>CSPRNG and TRNG</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2.2.1.1.4-2</t>
+          <t>2.2.1.1.3-3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -789,50 +2591,49 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>The system shall extract the received 128-bit AES-CMAC authentication tag from the embedded footer of each received SOW1 video frame.</t>
+          <t>The system shall use a CSPRNG compliant with NIST SP 800-90A and seeded by a hardware TRNG to generate the 256-bit session key.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>MVC-106572. Test: CS-SOW1-019.</t>
+          <t>MVC-106560. Test: CS-SOW1-011.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>where exactly is the footer in the frame (which line, which bytes, byte order) and what is its length when the tag is absent? Defined in the Samsung note (not in the repo).</t>
+          <t>which DRBG and which TRNG interface is used, and is there evidence for SP 800-90A conformity and for the quality of the TRNG?</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>without the layout the extraction cannot be implemented or tested. Add the layout reference to the technical requirement.</t>
+          <t>"compliant with SP 800-90A" is a design property, not testable from outside. Proposal: change the method to Review (design and code evidence), and keep a test only for the failure behaviour.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>extraction is internal. Either read the extracted value with Lauterbach, or infer it from acceptance, which makes it the same test as 119709. Missing or short footers need a defined reaction (the SRS says reject, MVC-108134).</t>
+          <t>black-box tests can only show uniqueness. Failure injection (TRNG returns an error) can be done by forcing the return value with Lauterbach.</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>frame 1 to 17 have no tag (entry 1). The tag is described as 128 bits; whether the footer ever carries more (padding, status bits) is unknown.</t>
+          <t>SP 800-90A defines the DRBG, not the entropy source (SP 800-90B). Reseeding is not mentioned. Proposal: add a reseed rule.</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>this is an implementation step of 119709, not a security property by itself. Proposal: keep it at technical level, or merge into 119709.</t>
+          <t>overlaps the debug requirement MVC-103050 (also TRNG). Both depend on the same driver.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MVC-106572. SRS 23.2.5.1 (MVC-108140, 108129, 108134, 108132).</t>
+          <t>MVC-106560. SRS MVC-108106, 108109. Also SRS 23.1.1.2 (DTLS) uses the same source.</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>SIM: frame with known tag T = 0x00112233...  in the footer
-Lauterbach: read the extracted-tag buffer          -&gt; expect T
-repeat with 10 different tags                      -&gt; expect each equal (not hard-coded)
-SIM: frame without footer / short footer / garbage -&gt; expect: rejected, no crash, log entry
+          <t>Review: CSPRNG library = SP 800-90A DRBG? seed source = SoC TRNG API? -&gt; collect evidence
+Lauterbach: breakpoint on TRNG read, force error  -&gt; expect: session aborted, no key block on I2C (Saleae)
+collect 1000 SSKs via SIM                        -&gt; expect: no repeat
 Decision: OPEN
 ---</t>
         </is>
@@ -842,9 +2643,9 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
     </row>
     <row r="5" ht="240" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -852,17 +2653,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>MVC-103033</t>
+          <t>MVC-103034</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Calculate frame CMAC</t>
+          <t>Transmit encrypted SSK</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2.2.1.1.4-3</t>
+          <t>2.2.1.1.3-5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -877,51 +2678,50 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>The system shall calculate a 128-bit AES-CMAC tag over the selected rows of each video frame using the active 256-bit session key.</t>
+          <t>The system shall transmit the 2048bit Encrypted Session Key and row information to the Imager for secure session establishment.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>MVC-106583. Test: CS-SOW1-020.</t>
+          <t>MVC-106578. Test: CS-SOW1-014.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>exactly which bytes form the message: only the pixel and embedded data of the selected rows, or also the line headers/footers and CSI-2 packet bytes? Row numbering base? (Samsung note.)</t>
+          <t>how does SOW2 learn that the imager accepted the key block? What is "the expected response" used in 103046?</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>two implementations could calculate different tags for the same frame. Add the exact message construction and a test vector from Samsung.</t>
+          <t>no requirement says when a session counts as established. Without it 119708, 103046 and 103044 cannot be tested. Proposal: add one requirement, for example "the session is established when the imager acknowledges the key block and the first valid tagged frame is received".</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>a reference calculation (PyRef) works only if the tester knows the SSK and the exact input. With the SIM it is possible. A known-answer test vector from Samsung would make it independent of the SIM.</t>
+          <t>capturing the write on the SoC to deserializer I2C bus is possible. The message layout comes from the Samsung note.</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>AES-CMAC with a 256-bit key is standard (NIST SP 800-38B, AES-256). The requirement says "128-bit tag": full output, not truncated, should be stated. The interval rule in MVC-108741 (at least 10 or 30 rows) exists so the imager finishes one row before the next. The host side has no stated rule on how fast it must compute.</t>
+          <t>the Volvo spec configures "I2C CRC ON" for the C1-sample, so the transfer is protected by CRC at transport level. The key block of about 256 bytes may need several I2C writes: partial writes need a defined reaction.</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>it also says "selected rows", which are defined in four other requirements (103055 note, 106576, 108741, 106574). Better to give the row selection its own concept requirement and reference it here.</t>
+          <t>the concept says "transmit ... to the Imager", the technical requirement adds "over the I2C interface". Fine.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>MVC-106583. SRS MVC-108122, 108121, 108118.</t>
+          <t>MVC-106578. SRS MVC-108146, 108145.</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>TE-1190: capture a real frame (raw rows)
-PyRef:   tag_ref = AES256-CMAC(SSK, selected rows as defined)
-SIM:     send the frame with tag_ref  -&gt; expect: accepted
-modify 1 byte in a selected row, keep tag_ref -&gt; expect: rejected
-modify 1 byte in a NOT selected row, keep tag_ref -&gt; expect: accepted (shows the coverage limit, record it)
+          <t>Saleae: after authentication OK, capture the writes to the imager key register(s) -&gt; expect: encrypted block, correct length
+check order: auth read -&gt; verify -&gt; key write (no key write before auth OK)
+SIM acknowledges                  -&gt; Lauterbach: state = SESSION_ACTIVE
+SIM stays silent                  -&gt; state != SESSION_ACTIVE
 Decision: OPEN
 ---</t>
         </is>
@@ -931,9 +2731,9 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
     </row>
     <row r="6" ht="240" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -941,17 +2741,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MVC-103031</t>
+          <t>MVC-103051</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Extract frame counter</t>
+          <t>Terminate authentication</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2.2.1.1.4-6</t>
+          <t>2.2.1.1.2-4</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -966,50 +2766,51 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>The system shall extract the video frame counter from the embedded header data of each received SOW1 video frame and use the counter value for freshness validation.</t>
+          <t>The system shall terminate the Imager authentication process if authentication is not successfully completed within the configured maximum number of retry attempts</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>MVC-113726 (extract) and MVC-106575 (verify freshness, ordering and sequence). Tests: CS-SOW1-025, CS-SOW1-023.</t>
+          <t>MVC-106569. Test: CS-SOW1-006.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>size of the counter (bits), start value, behaviour at wrap-around, and whether the imager resets it at every stream start. (Samsung note.)</t>
+          <t>after termination, what does the ECU do: stay without video, try again later, or enter a safe state? And when is another attempt allowed (only after reset?).</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>the window rule in 113703 cannot be checked at the wrap without the width. Add width and wrap behaviour.</t>
+          <t>this is a cybersecurity failure that can switch off a camera image. Define the system reaction together with the FuSa team. Proposal: add the reaction and the rule for a later new attempt.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>the counter is internal. Read it with Lauterbach. Boundary tests need the SIM to send chosen values, in particular near the maximum.</t>
+          <t>the end state (UNAUTHENTICATED, no key sent, no trusted video) is observable with Lauterbach, Saleae and Wireshark. "Does not retry indefinitely" needs a long observation time (define it).</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>the counter is only protected by the CMAC if the header line is among the selected rows (start row 0, MVC-106576). If it is not, the counter can be forged freely. State this dependency here.</t>
+          <t>the concept says "configured maximum", the technical requirement says a fixed "three". Fixed or configurable, and where is it configured?</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>"extract and use for freshness" is two things, and the concept requirement is satisfied by two technical requirements, one for each. The "use" part (MVC-106575, freshness, ordering and sequence) overlaps MVC-113727, which belongs to 113703 (entry 6). Proposal: keep only the extraction here, and let 113703 own the validity rule.</t>
+          <t>see 103053.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>MVC-113726 and MVC-106575 (CS-SOW1-023 has no entry of its own below, it is covered here and in entry 6). SRS MVC-108099.</t>
+          <t>MVC-106569. SRS MVC-108124 (terminate if data incomplete) is similar but not the same.</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>SIM: frames with counter 1,2,3,...,N
-Lauterbach: read extracted counter after each frame   -&gt; expect: equal to SIM value
-SIM: counter = 0xFFFF.. then 0 (width as defined)    -&gt; expect: defined wrap handling
-SIM: header missing / short                           -&gt; expect: rejected, log entry
+          <t>SIM never gives valid data; reset
+Saleae: wait 60 s after the last retry       -&gt; expect: no further auth requests, no key write
+Lauterbach: read auth state                  -&gt; expect: UNAUTHENTICATED
+SIM then sends frames with a valid tag       -&gt; expect: still rejected (see 119708)
+Power cycle                                  -&gt; expect: a new authentication attempt starts
 Decision: OPEN
 ---</t>
         </is>
@@ -1019,9 +2820,9 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
     </row>
     <row r="7" ht="240" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1029,72 +2830,517 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>MVC-103044</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Terminate session establishment</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.3-8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>The system shall terminate secure session establishment if a secure session is not successfully established after three retry attempts.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106581. Test: CS-SOW1-017.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>the reaction after termination (no video, new full authentication later, safe state). Same question as entry 12.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>define what happens next and whether the three retries are repeated after a full new authentication.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>the end state is observable: no active session, no more writes, the key not used.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>the SRS says partially established session data must be invalidated (MVC-108149). Check that the SSK from the failed attempt is erased, with Lauterbach reading the key buffer.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>NONE.</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106581. SRS MVC-108149, 108158.</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>SIM: never acknowledges the key block
+Saleae: after the last retry, wait 60 s            -&gt; expect: no more key writes
+Lauterbach: session state = INACTIVE; read key buffer -&gt; expect: zeroed
+SIM sends tagged frames                             -&gt; expect: rejected
+trigger a new attempt (reset)                       -&gt; expect: authentication starts again
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="240" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MVC-103063</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Root key in OTP</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.1-1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>The system shall store the trusted 2048bit Samsung Root Public Key in OTP memory.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106562. Test: CS-SOW1-001.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>which OTP zone holds it, and who programs it (Mekra factory, Ambarella) and when? The SRS secure-boot requirement mentions OTP "zone 7 [X]" as an open choice. The CV22FS manual describes the power-on-configuration OTP as factory-set and not user-accessible, and I did not find a customer-key zone in the manuals I have.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>the test and the production flow depend on the zone. Proposal: name the zone and add "and shall prevent modification, replacement or deletion" (the technical verification criteria already test immutability, the requirement does not state it; SRS MVC-108142 does).</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>OTP is write-once, so the "cannot be overwritten" test destroys a sample. Test samples need a test root key, because Samsung's private key is not available. A production sample can only be checked by comparing a hash if OTP is read-locked.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>the concept says OTP, SRS MVC-108143 says "protected non-volatile storage". Not the same. RSA-2048 public key = 256-byte modulus plus exponent: confirm the free OTP size.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>the technical requirement has the same text as the concept requirement.</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106562. SRS 23.2.1 (MVC-108143, 108142, 108144). The secure-boot key (SRS 23.4) is a different root: make sure both are tracked.</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Lauterbach: read OTP zone X (if allowed in this lifecycle) -&gt; SHA-256(key) == fingerprint of the Samsung root key
+Lauterbach/SW: write to OTP zone X                          -&gt; expect: rejected or locked
+power cycle + reset                                          -&gt; read again, expect same value
+SIM signs auth data with the matching private key (test build)  -&gt; authentication passes
+SIM signs with another key                                   -&gt; authentication fails
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="240" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>MVC-103053</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Retry authentication</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.2-3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>The system shall retry the Imager authentication process up to three times if the expected authentication data is failed to be received.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106566. Test: CS-SOW1-005.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>three retries (4 requests) or three attempts (3 requests)? MVC-106569 says "three authentication attempts". One number is needed. Also the timeout per attempt and the time between attempts.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>a test that counts requests on the bus cannot pass or fail without it. Proposal: "N attempts in total, each with timeout T".</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>counting requests with Saleae is easy. Withholding the answer needs the SIM or a way to cut the I2C response. Timing cannot be checked until T exists.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>what is "not received": no ACK, partial answer, timeout, or malformed? A complete but invalid answer is a signature failure (reject at once?). Define.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>the retry rule is split over two requirements (103053 retry, 103051 terminate) that use different words ("up to three retries" and "configured maximum").</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106566. SRS MVC-108124, 108126.</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>SIM: do not answer the authentication read; reset
+Saleae: count auth read requests until SOW2 stops   -&gt; expect: N (as decided)
+SIM: answer correctly on request 2                  -&gt; expect: authentication continues
+Saleae: measure time between requests               -&gt; expect: equals T (once defined)
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="240" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MVC-103046</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Retry session establishment</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.3-7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>The system shall retry secure session establishment up to three times if the expected response is failed to be received.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106567. Test: CS-SOW1-016.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>what is the "expected response"? Timeout per try? On each retry, is the same encrypted block sent again, or a new SSK and a new block?</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>define response, timeout and what is sent again. Proposal: a new block (re-encrypted) with the same SSK, or a new SSK, but state it.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>counting retries with Saleae, SIM withholding the response. Nothing can be checked until the response is defined (entry 17).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>"three retries" is consistent with 103044 and with the technical requirements.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>NONE.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106567. SRS MVC-108149 (timeout or retry limit).</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>SIM: accept authentication, do not answer the key block
+Saleae: count key block writes     -&gt; expect: 1 + 3 (as decided)
+SIM: answer on the 2nd write       -&gt; expect: session established
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="240" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>MVC-103036</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>New session after triggers</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.3-9</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>The system shall require establishment of a new secure session, including full SOW1 authentication and generation of a new session key (SSK), after session expiry, system reset, system restart, session termination, or detection of a security failure.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106573. Test: CS-SOW1-018.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>• Session lifetime: what is the expiry time? No requirement defines it.
+• "Security failure": which events (one bad CMAC frame? ten? an I2C error?). SRS MVC-108158 says "video authentication failure requiring session recovery", which has no definition either.
+• "System reset" and "system restart": what is the difference?</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>two of the five triggers cannot be tested without these definitions. This also conflicts with 119710 (reject the frame and continue, SRS MVC-108105): the line between "reject one frame" and "start a new session" is missing. Proposal: define a lifetime, a failure threshold (for example N bad frames within T seconds) and merge reset and restart.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>each trigger can be tested alone, as the verification criteria already say. Old key must be rejected afterwards: the SIM keeps sending frames with the old key.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>renegotiating while the camera streams: what happens to the video during the new authentication? Interruption time is not limited.</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>several requirements in one (five triggers). Consider one requirement per trigger group, or keep it and give each trigger its own test (the technical test does this).</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106573. SRS MVC-108156, 108158, 108151.</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>for trigger in [expiry, reset, restart, termination, security failure]:
+    establish session; SIM sends frames with SSK_old -&gt; accepted
+    fire the trigger
+    Saleae: new auth read + new key block     -&gt; expect: yes
+    SIM decrypts the new block: SSK_new != SSK_old
+    SIM sends frames with SSK_old             -&gt; expect: rejected
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="240" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>MVC-113703</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Freshness window</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2.2.1.1.4-7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>CAL 2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>The system shall reject duplicated, stale, or out-of-order SOW1 video frames based on a 3-frame freshness window and shall accept a frame only when its frame counter satisfies LastAcceptedCounter &lt; ReceivedCounter ≤ LastAcceptedCounter + 3.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>MVC-113727. Test: CS-SOW1-026.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>counter width and wrap (entry 5). Initial LastAcceptedCounter after a new session.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>• Impact: if more than 3 consecutive frames are lost (link problem, brief disturbance, SoC load), every later valid frame has a counter above LastAcceptedCounter + 3 and is rejected. The stream stays dead until a new session. For a safety-relevant camera that is an availability problem.
 • Proposal: define a recovery: after N consecutive frames rejected only because of the window, but with valid CMAC, re-synchronise LastAcceptedCounter. Or end the session and renegotiate, and say which.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>the boundaries in the requirement are good and easy to test with the SIM (equal, lower, +1, +2, +3, +4). Wrap-around and the first frame of a session cannot be tested until they are defined.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>• Order of checks: update LastAcceptedCounter only after the CMAC passed. Otherwise a forged frame with a high counter can push the window forward and block genuine frames. State the order.
 • No behaviour for the first frame of a session.</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>NONE.</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>MVC-113727. SRS MVC-108099, 108104, 108102. The recovery behaviour is in no requirement.</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>SIM: frames with valid CMAC, counters:  10 accepted
 send 10 (dup)         -&gt; reject        send 9 (stale)  -&gt; reject
@@ -1106,85 +3352,344 @@
 ---</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8" ht="240" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="240" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>MVC-119710</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Reject frame on failure</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.4-5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>The system shall reject any received SOW1 video frame if AES-CMAC verification fails.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106564. Test: CS-SOW1-022.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>"Reject" is not defined: dropped, replaced by the previous frame, or shown with a flag? This is a camera that drives a display, so a defined reaction matters. Proposal: state the reaction (drop the frame, count it, log it, keep processing the next frames, which SRS MVC-108105 already says) and when repeated failures start a new session (see 103036).</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>the observable is the same as 119709. Define it once: dropped frame counter and log event. The VC step "does not cause the same invalid frame to be re-submitted" needs a defined internal buffer to look at.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>no limit on how many bad frames are tolerated before the stream is treated as an attack. A single corrupted frame from EMI on the cable would also fail the CMAC (the link has CRC, but the check here is separate). Question: do random corruption and a forged frame get the same reaction?</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>overlaps 119709 (see entry 1). Overlaps SRS MVC-108116.</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106564 (link both ways). SRS MVC-108116, 108108, 108105. Same upstream as 119709.</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>SIM: send 10 good frames, 1 frame with wrong tag, 10 good frames
+Wireshark: RTP shows 20 frames, the bad one missing        -&gt; expect: bad frame not forwarded
+UART log: 1 "CMAC failed" entry                            -&gt; expect: logged
+Lauterbach: read dropped-frame counter                     -&gt; expect: 1
+SIM: send 1000 frames, each with a wrong tag                -&gt; expect: defined reaction (new session or stay up) once decided
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="240" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>MVC-119714</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>No commands before authentication</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.5-1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>The system shall not transmit SOW1 control commands before successful SOW1 device authentication.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>MVC-109119 ("protected SOW1 control commands"). Test: CS-SOW1-027.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>which commands are "control commands"? The imager has to be configured over I2C (for example the settings files in SOW1/Imager Settings/) and the authentication itself is I2C traffic. Which I2C writes are allowed before authentication?</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>read literally, the requirement forbids the writes needed to start the camera. The technical text says "protected" commands, the SRS too. Proposal: list the protected commands, or list the allowed pre-authentication ones, and use the word "protected" at concept level.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Saleae can list all writes to the imager address. The pass criterion needs the list from the SIQ.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>the Volvo spec does not mention any protected command channel. See entry 23.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>concept says "SOW1 control commands", technical says "protected SOW1 control commands": two terms.</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>MVC-109119. SRS MVC-108169.</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>reset; SIM does not complete authentication
+trigger a protected command (command source to confirm)
+Saleae: list all I2C writes to the imager          -&gt; expect: only the allowed pre-auth writes, no protected command
+repeat after authentication failure and before the key block was acknowledged
+complete authentication + session; trigger again    -&gt; expect: command sent
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="240" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>MVC-113706</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Do not expose SSK</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.3-6</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>The system shall not expose the active session key through any accessible interface during the active secure session.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106571. Test: CS-SOW1-015.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>"any accessible interface" must be a list. Proposal: UART, JTAG (when unlocked), logs, SOME/IP and DTLS diagnostics, memory dumps, I2C, SPI flash.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>a negative test. It needs a list of interfaces and the SSK value (from the SIM) to search for.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>the SRS keeps the key in DRAM (MVC-108164). An authorised debug session (secure debug requirements) lets Lauterbach read DRAM, so the key would be readable through the debug interface. Either the debug unlock must exclude the key region, or this is an accepted exception. Please decide.</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>the technical requirement duplicates the text. SRS has related requirements (MVC-108164, 108163, 108154, 108157).</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106571. SRS MVC-108164, 108163, 108154, 108157. Related to the debug requirements and to DRAM protection (SRS 23.5).</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>SIM: get SSK value (decrypt the key block)
+JTAG locked: attach with Lauterbach -&gt; expect: denied
+search captures for the SSK bytes: I2C (Saleae), Ethernet (Wireshark), UART log -&gt; expect: not found
+trigger failures (bad frame, failed session) -&gt; read logs and diagnostic responses -&gt; expect: no key bytes
+authorised debug unlocked: Lauterbach read of the key region in DRAM -&gt; record result; expect: blocked, or an accepted exception
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="240" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>MVC-119708</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>No trust before session</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2.2.1.1.4-1</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>CAL 2</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>The system shall not accept SOW1 secured video stream data as trusted before successful SOW1 device authentication and secure session establishment.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>MVC-109120. Test: CS-SOW1-024.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>what does the system do with video that is "not trusted"? Drop it (no image for the driver) or pass it with an "untrusted" flag? This is a camera for the vehicle; both the safety and security teams must agree.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>"not accept as trusted" can be implemented in two very different ways. Define the reaction and who evaluates it (the downstream display side, the vehicle ECU, or SOW2). Cross-check with frames 1 to 17 (entry 1).</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>the observable is the outgoing stream (Wireshark on RTP) and a status signal if one exists. If "untrusted" is only an internal flag, there is nothing to check from outside.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>"secure session establishment" has no definition of when it is complete (imager acknowledgement? first good CMAC?). See entry 17.</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>NONE.</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>MVC-109120. SRS MVC-108138. The reaction is in no requirement.</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>reset, SIM does not answer authentication
 SIM: send frames (valid CMAC, any key)        -&gt; Wireshark: no trusted video out / flagged as untrusted
@@ -1195,616 +3700,169 @@
 ---</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="240" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103063</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Root key in OTP</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.1-1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="240" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>MVC-113702</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Command counter</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.5-4</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>CAL 2</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>The system shall store the trusted 2048bit Samsung Root Public Key in OTP memory.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106562. Test: CS-SOW1-001.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>which OTP zone holds it, and who programs it (Mekra factory, Ambarella) and when? The SRS secure-boot requirement mentions OTP "zone 7 [X]" as an open choice. The CV22FS manual describes the power-on-configuration OTP as factory-set and not user-accessible, and I did not find a customer-key zone in the manuals I have.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>the test and the production flow depend on the zone. Proposal: name the zone and add "and shall prevent modification, replacement or deletion" (the technical verification criteria already test immutability, the requirement does not state it; SRS MVC-108142 does).</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>OTP is write-once, so the "cannot be overwritten" test destroys a sample. Test samples need a test root key, because Samsung's private key is not available. A production sample can only be checked by comparing a hash if OTP is read-locked.</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>the concept says OTP, SRS MVC-108143 says "protected non-volatile storage". Not the same. RSA-2048 public key = 256-byte modulus plus exponent: confirm the free OTP size.</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>the technical requirement has the same text as the concept requirement.</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106562. SRS 23.2.1 (MVC-108143, 108142, 108144). The secure-boot key (SRS 23.4) is a different root: make sure both are tracked.</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Lauterbach: read OTP zone X (if allowed in this lifecycle) -&gt; SHA-256(key) == fingerprint of the Samsung root key
-Lauterbach/SW: write to OTP zone X                          -&gt; expect: rejected or locked
-power cycle + reset                                          -&gt; read again, expect same value
-SIM signs auth data with the matching private key (test build)  -&gt; authentication passes
-SIM signs with another key                                   -&gt; authentication fails
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>The system shall include a monotonically increasing Counter in each SOW1 control command transmitted.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>MVC-109121. Test: CS-SOW1-030.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>counter width, start value, behaviour at the maximum, and does the imager check it?</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>"monotonically" allows equal values. Proposal: "strictly increasing" and no reuse within the session (SRS MVC-108161). The counter restarts with each session because the key changes: say so. State the wrap rule (new session before wrap).</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>with Saleae the counter can be read from many commands. The maximum value case needs a test hook to preset the counter.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>replay protection exists only if the imager rejects old counters. If it does not check, the counter protects nothing. Same open point as 113701.</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>see 113701.</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>MVC-109121. SRS MVC-108159, 108161.</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>send 100 protected commands; Saleae: read counter of each -&gt; expect: strictly increasing, no repeats
+reset (new session)                                      -&gt; counter restarts as defined
+Lauterbach: preset counter near the max; send commands   -&gt; expect: defined behaviour (new session before wrap)
+if the imager checks: replay an old command (old counter) -&gt; expect: rejected
 Decision: OPEN
 ---</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10" ht="240" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>MVC-107642</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Authenticate imager</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.2-1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="240" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>MVC-103057</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Generate 256-bit SSK</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.3-2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CAL 2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>The system shall authenticate the Imager by verifying the digital signature received from the Imager over the I2C interface using the provisioned Samsung Root Public Key.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106561, 106565, 106563. Tests: CS-SOW1-002, 003, 004.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>• SIQ-1 (Samsung): define Device_n, KID, Sig_device. The Volvo spec says the signature covers "the device specific RSA public key along with the Device ID". The technical requirement says "over Device_n and KID". Is Device_n the key modulus and KID the Device ID? And is KID a key or algorithm identifier? The SRS (MVC-108135, 108136) lets KID select the signature scheme and hash.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>if the signed message is not defined byte for byte, SOW2 and the test cannot agree. Add the exact signed message and encoding to the technical requirement.</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>needs signed data from the test root key. Negative cases (one field changed, other key) need the SIM.</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>• The signature in the imager is a fixed value, stored in OTP and read over I2C. I found no challenge-response in the Volvo flow. A fake camera can copy the genuine data (it is not secret) and pass step 2. What stops it is that it does not hold the private key, so it cannot decrypt the session key and cannot produce a valid CMAC. Until the first valid tagged frame (frame 18 or later) SOW2 has no proof that the camera owns the key. Please confirm this is understood and accepted.
-• The concept fixes the scheme (107641), while the SRS makes KID select the scheme. See entry 10.</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>the concept requirement is verified by three technical requirements (request, verify, scheme). That is fine, but the pass criteria overlap. Keep each test about one thing.</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>concept to technical: three links. SRS 23.2.2 and 23.2.3 (MVC-108133, 108131, 108126, 108124, 108113, 108111).</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>SIM: serve genuine data (Device_n, KID, Sig_device signed by test root)
-Saleae: capture auth read           -&gt; expect: SOW2 asks for the fields; then accepts; key block follows
-SIM: flip 1 bit in Device_n / KID / Sig_device (one run each) -&gt; expect: rejected, no key block sent
-SIM: signature from another key     -&gt; expect: rejected
-SIM: copy genuine data, no private key (replay) -&gt; expect: auth accepted, but no valid CMAC frame ever -&gt; frames rejected
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="240" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>MVC-107641</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>RSASSA-PSS with SHA-256</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.2-2</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>The system shall use RSASSA-PSS with SHA-256 to verify the Imager's digital signature.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106563 (no link back in Polarion). Test: CS-SOW1-004.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>PSS parameters: salt length, mask generation function (MGF1 with SHA-256?). And the SRS lets KID choose scheme and hash (MVC-108135, 108120). Is PSS with SHA-256 the only supported one?</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>if only one scheme exists, tell the SRS to drop the selection by KID. If KID selects among several, this requirement must say which values of KID are accepted.</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>partly an inspection (the technical verification criteria say "implementation inspection"). The black-box part: signatures made with PKCS#1 v1.5, other hashes or other salt lengths must fail. The salt-length case cannot be written until the salt is defined.</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>salt length, MGF and exponent are not stated.</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>it is a property of the verification in 107642, not a stand-alone behaviour. Proposal: merge into 107642 or keep as a technical detail.</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>the technical requirement MVC-106563 does not link to it (only to 107642). Add the link. SRS MVC-108120, 108135, 108136.</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Code review: verify call = RSASSA-PSS + SHA-256 (CS-SOW1-004 step 1)
-PyRef: sign (Device_n||KID) with test root key:
-   PSS+SHA-256   -&gt; SIM serves -&gt; expect: accepted
-   PKCS#1 v1.5   -&gt; expect: rejected
-   PSS+SHA-1 or SHA-384 -&gt; expect: rejected
-   PSS+SHA-256, other salt length -&gt; expect: as defined (once the salt is fixed)
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12" ht="240" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103053</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Retry authentication</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.2-3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>The system shall retry the Imager authentication process up to three times if the expected authentication data is failed to be received.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106566. Test: CS-SOW1-005.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>three retries (4 requests) or three attempts (3 requests)? MVC-106569 says "three authentication attempts". One number is needed. Also the timeout per attempt and the time between attempts.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>a test that counts requests on the bus cannot pass or fail without it. Proposal: "N attempts in total, each with timeout T".</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>counting requests with Saleae is easy. Withholding the answer needs the SIM or a way to cut the I2C response. Timing cannot be checked until T exists.</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>what is "not received": no ACK, partial answer, timeout, or malformed? A complete but invalid answer is a signature failure (reject at once?). Define.</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>the retry rule is split over two requirements (103053 retry, 103051 terminate) that use different words ("up to three retries" and "configured maximum").</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106566. SRS MVC-108124, 108126.</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>SIM: do not answer the authentication read; reset
-Saleae: count auth read requests until SOW2 stops   -&gt; expect: N (as decided)
-SIM: answer correctly on request 2                  -&gt; expect: authentication continues
-Saleae: measure time between requests               -&gt; expect: equals T (once defined)
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="240" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103051</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Terminate authentication</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.2-4</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>The system shall terminate the Imager authentication process if authentication is not successfully completed within the configured maximum number of retry attempts</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106569. Test: CS-SOW1-006.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>after termination, what does the ECU do: stay without video, try again later, or enter a safe state? And when is another attempt allowed (only after reset?).</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>this is a cybersecurity failure that can switch off a camera image. Define the system reaction together with the FuSa team. Proposal: add the reaction and the rule for a later new attempt.</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>the end state (UNAUTHENTICATED, no key sent, no trusted video) is observable with Lauterbach, Saleae and Wireshark. "Does not retry indefinitely" needs a long observation time (define it).</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>the concept says "configured maximum", the technical requirement says a fixed "three". Fixed or configurable, and where is it configured?</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>see 103053.</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106569. SRS MVC-108124 (terminate if data incomplete) is similar but not the same.</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>SIM never gives valid data; reset
-Saleae: wait 60 s after the last retry       -&gt; expect: no further auth requests, no key write
-Lauterbach: read auth state                  -&gt; expect: UNAUTHENTICATED
-SIM then sends frames with a valid tag       -&gt; expect: still rejected (see 119708)
-Power cycle                                  -&gt; expect: a new authentication attempt starts
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14" ht="240" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103040</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Extract device public key</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.3-1</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Following successful authentication, The system shall extract 2048-bit device public key from the Imager's authentication data.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106577. Test: CS-SOW1-012.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>format of the key in the data (modulus only, fixed exponent?).</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>add sanity checks (length 2048 bits, odd modulus, exponent as defined) before the key is used.</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>the extracted key is internal. Indirect check: SOW2 encrypts with it, and the SIM decrypts with its private key. If decryption works, the right key was used. Wrong-size or malformed keys signed with the test root key are easy to create.</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>the key is covered by the signature only if Device_n is the key modulus (SIQ in entry 9). If it is not covered, a key swap is possible.</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>The system shall generate a 256-bit cryptographically random session key (SSK) following successful Imager authentication.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106568. Test: CS-SOW1-010.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>"new key for every session" is in the verification criteria but not in the requirement text. Add it (SRS MVC-108110 says it).</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>the SSK is only visible through the SIM (decrypting the key block). With a real imager it cannot be seen. Randomness cannot be proven by test, only checked for repeats.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>NONE.</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106577. SRS 23.2.4.4 (MVC-108153) uses "the authenticated SOW1 Device public key".</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>SIM: device key K1, signed by test root; authentication OK
-SIM: decrypt the key block that SOW2 writes with K1_priv  -&gt; expect: success (proves K1 was used)
-SIM: key of 1024 or 4096 bits, valid signature             -&gt; expect: rejected, no key block sent
-SIM: truncated or all-zero key, valid signature            -&gt; expect: rejected
-Lauterbach (optional): compare the key buffer with K1
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="240" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103057</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Generate 256-bit SSK</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.3-2</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>The system shall generate a 256-bit cryptographically random session key (SSK) following successful Imager authentication.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106568. Test: CS-SOW1-010.</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>"new key for every session" is in the verification criteria but not in the requirement text. Add it (SRS MVC-108110 says it).</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>the SSK is only visible through the SIM (decrypting the key block). With a real imager it cannot be seen. Randomness cannot be proven by test, only checked for repeats.</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>NONE.</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>overlaps 103042 (how it is generated) and 103036 (new session needs a new key). Proposal: keep "256-bit, new each session" here and "how" in 103042.</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>MVC-106568. SRS MVC-108107, 108110.</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>loop 1000 times: reset -&gt; authenticate -&gt; SIM decrypts the key block -&gt; store SSK
 check: length = 32 bytes; no two SSKs equal; bit balance roughly 50 percent
@@ -1813,172 +3871,261 @@
 ---</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16" ht="240" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103042</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>CSPRNG and TRNG</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.3-3</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="240" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>MVC-103031</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Extract frame counter</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.4-6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>CAL 2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>The system shall use a CSPRNG compliant with NIST SP 800-90A and seeded by a hardware TRNG to generate the 256-bit session key.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106560. Test: CS-SOW1-011.</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>which DRBG and which TRNG interface is used, and is there evidence for SP 800-90A conformity and for the quality of the TRNG?</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>"compliant with SP 800-90A" is a design property, not testable from outside. Proposal: change the method to Review (design and code evidence), and keep a test only for the failure behaviour.</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>black-box tests can only show uniqueness. Failure injection (TRNG returns an error) can be done by forcing the return value with Lauterbach.</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>SP 800-90A defines the DRBG, not the entropy source (SP 800-90B). Reseeding is not mentioned. Proposal: add a reseed rule.</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>overlaps the debug requirement MVC-103050 (also TRNG). Both depend on the same driver.</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106560. SRS MVC-108106, 108109. Also SRS 23.1.1.2 (DTLS) uses the same source.</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Review: CSPRNG library = SP 800-90A DRBG? seed source = SoC TRNG API? -&gt; collect evidence
-Lauterbach: breakpoint on TRNG read, force error  -&gt; expect: session aborted, no key block on I2C (Saleae)
-collect 1000 SSKs via SIM                        -&gt; expect: no repeat
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>The system shall extract the video frame counter from the embedded header data of each received SOW1 video frame and use the counter value for freshness validation.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>MVC-113726 (extract) and MVC-106575 (verify freshness, ordering and sequence). Tests: CS-SOW1-025, CS-SOW1-023.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>size of the counter (bits), start value, behaviour at wrap-around, and whether the imager resets it at every stream start. (Samsung note.)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>the window rule in 113703 cannot be checked at the wrap without the width. Add width and wrap behaviour.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>the counter is internal. Read it with Lauterbach. Boundary tests need the SIM to send chosen values, in particular near the maximum.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>the counter is only protected by the CMAC if the header line is among the selected rows (start row 0, MVC-106576). If it is not, the counter can be forged freely. State this dependency here.</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>"extract and use for freshness" is two things, and the concept requirement is satisfied by two technical requirements, one for each. The "use" part (MVC-106575, freshness, ordering and sequence) overlaps MVC-113727, which belongs to 113703 (entry 6). Proposal: keep only the extraction here, and let 113703 own the validity rule.</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>MVC-113726 and MVC-106575 (CS-SOW1-023 has no entry of its own below, it is covered here and in entry 6). SRS MVC-108099.</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>SIM: frames with counter 1,2,3,...,N
+Lauterbach: read extracted counter after each frame   -&gt; expect: equal to SIM value
+SIM: counter = 0xFFFF.. then 0 (width as defined)    -&gt; expect: defined wrap handling
+SIM: header missing / short                           -&gt; expect: rejected, log entry
 Decision: OPEN
 ---</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="240" customHeight="1">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="240" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>MVC-113705</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Extract tag from footer</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.4-2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>The system shall extract the received 128-bit AES-CMAC authentication tag from the embedded footer of each received SOW1 video frame.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106572. Test: CS-SOW1-019.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>where exactly is the footer in the frame (which line, which bytes, byte order) and what is its length when the tag is absent? Defined in the Samsung note (not in the repo).</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>without the layout the extraction cannot be implemented or tested. Add the layout reference to the technical requirement.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>extraction is internal. Either read the extracted value with Lauterbach, or infer it from acceptance, which makes it the same test as 119709. Missing or short footers need a defined reaction (the SRS says reject, MVC-108134).</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>frame 1 to 17 have no tag (entry 1). The tag is described as 128 bits; whether the footer ever carries more (padding, status bits) is unknown.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>this is an implementation step of 119709, not a security property by itself. Proposal: keep it at technical level, or merge into 119709.</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106572. SRS 23.2.5.1 (MVC-108140, 108129, 108134, 108132).</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>SIM: frame with known tag T = 0x00112233...  in the footer
+Lauterbach: read the extracted-tag buffer          -&gt; expect T
+repeat with 10 different tags                      -&gt; expect each equal (not hard-coded)
+SIM: frame without footer / short footer / garbage -&gt; expect: rejected, no crash, log entry
+Decision: OPEN
+---</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="240" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>MVC-103055</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Encrypt SSK and Row_info</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2.2.1.1.3-4</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>CAL 2</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>The system shall encrypt the session key and selected row information using the 2048-bit device public key with RSAES-OAEP and SHA-256. (Note: row information format is defined by Samsung, chapter 5 Key sharing of the S5K3B6SA cybersecurity application note.)</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>MVC-106580, 106576, 108741, 106574. Tests: CS-SOW1-013, 007, 008, 009.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>message layout (SSK, Row_info_00, Row_info_01, sizes, order), OAEP label (empty?) and MGF1 hash. The Samsung note is not in the repo.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>the layout is needed by implementation and test. Proposal: put the layout in the technical requirement.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>OAEP is randomised, so two encryptions of the same input differ. Compare plaintexts only: the SIM decrypts and checks the content. Injecting a known SSK needs a test hook (Lauterbach write before the encrypt call).</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>capacity check: RSA-2048 with OAEP and SHA-256 carries at most 256 − 2×32 − 2 = 190 bytes, so a 32-byte key plus the row information fits if the row information is small. The row rules in the technical requirements (start 0 or 1, interval at least 10 or 30 by output mode, and the formula start + 1 + (interval + 1) × (total − 1) ≤ ysize_image + ysize_embedded_data) depend on the output mode, so the mode must be known to the code that builds Row_info.</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>one concept requirement is satisfied by four technical requirements, three of which are about row selection and not about encryption. Proposal: a separate concept requirement for the row selection rules.</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>MVC-106580, 106576, 108741, 106574. SRS MVC-108153, 108145, 108165, 108166.</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>SIM (holds device private key): read the key block from I2C (Saleae / TE-1190)
 PyRef: RSA-OAEP decrypt, SHA-256, MGF1-SHA-256  -&gt; expect plaintext = SSK(32 B) || Row_info_00 || Row_info_01
@@ -1990,363 +4137,14 @@
 ---</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18" ht="240" customHeight="1">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103034</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Transmit encrypted SSK</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.3-5</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>The system shall transmit the 2048bit Encrypted Session Key and row information to the Imager for secure session establishment.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106578. Test: CS-SOW1-014.</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>how does SOW2 learn that the imager accepted the key block? What is "the expected response" used in 103046?</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>no requirement says when a session counts as established. Without it 119708, 103046 and 103044 cannot be tested. Proposal: add one requirement, for example "the session is established when the imager acknowledges the key block and the first valid tagged frame is received".</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>capturing the write on the SoC to deserializer I2C bus is possible. The message layout comes from the Samsung note.</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>the Volvo spec configures "I2C CRC ON" for the C1-sample, so the transfer is protected by CRC at transport level. The key block of about 256 bytes may need several I2C writes: partial writes need a defined reaction.</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>the concept says "transmit ... to the Imager", the technical requirement adds "over the I2C interface". Fine.</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106578. SRS MVC-108146, 108145.</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Saleae: after authentication OK, capture the writes to the imager key register(s) -&gt; expect: encrypted block, correct length
-check order: auth read -&gt; verify -&gt; key write (no key write before auth OK)
-SIM acknowledges                  -&gt; Lauterbach: state = SESSION_ACTIVE
-SIM stays silent                  -&gt; state != SESSION_ACTIVE
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="240" customHeight="1">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>MVC-113706</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Do not expose SSK</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.3-6</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>The system shall not expose the active session key through any accessible interface during the active secure session.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106571. Test: CS-SOW1-015.</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>"any accessible interface" must be a list. Proposal: UART, JTAG (when unlocked), logs, SOME/IP and DTLS diagnostics, memory dumps, I2C, SPI flash.</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>a negative test. It needs a list of interfaces and the SSK value (from the SIM) to search for.</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>the SRS keeps the key in DRAM (MVC-108164). An authorised debug session (secure debug requirements) lets Lauterbach read DRAM, so the key would be readable through the debug interface. Either the debug unlock must exclude the key region, or this is an accepted exception. Please decide.</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>the technical requirement duplicates the text. SRS has related requirements (MVC-108164, 108163, 108154, 108157).</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106571. SRS MVC-108164, 108163, 108154, 108157. Related to the debug requirements and to DRAM protection (SRS 23.5).</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>SIM: get SSK value (decrypt the key block)
-JTAG locked: attach with Lauterbach -&gt; expect: denied
-search captures for the SSK bytes: I2C (Saleae), Ethernet (Wireshark), UART log -&gt; expect: not found
-trigger failures (bad frame, failed session) -&gt; read logs and diagnostic responses -&gt; expect: no key bytes
-authorised debug unlocked: Lauterbach read of the key region in DRAM -&gt; record result; expect: blocked, or an accepted exception
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="240" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103046</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Retry session establishment</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.3-7</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>The system shall retry secure session establishment up to three times if the expected response is failed to be received.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106567. Test: CS-SOW1-016.</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>what is the "expected response"? Timeout per try? On each retry, is the same encrypted block sent again, or a new SSK and a new block?</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>define response, timeout and what is sent again. Proposal: a new block (re-encrypted) with the same SSK, or a new SSK, but state it.</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>counting retries with Saleae, SIM withholding the response. Nothing can be checked until the response is defined (entry 17).</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>"three retries" is consistent with 103044 and with the technical requirements.</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>NONE.</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106567. SRS MVC-108149 (timeout or retry limit).</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>SIM: accept authentication, do not answer the key block
-Saleae: count key block writes     -&gt; expect: 1 + 3 (as decided)
-SIM: answer on the 2nd write       -&gt; expect: session established
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="240" customHeight="1">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>MVC-103044</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Terminate session establishment</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.3-8</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>The system shall terminate secure session establishment if a secure session is not successfully established after three retry attempts.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106581. Test: CS-SOW1-017.</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>the reaction after termination (no video, new full authentication later, safe state). Same question as entry 12.</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>define what happens next and whether the three retries are repeated after a full new authentication.</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>the end state is observable: no active session, no more writes, the key not used.</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>the SRS says partially established session data must be invalidated (MVC-108149). Check that the SSK from the failed attempt is erased, with Lauterbach reading the key buffer.</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>NONE.</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>MVC-106581. SRS MVC-108149, 108158.</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>SIM: never acknowledges the key block
-Saleae: after the last retry, wait 60 s            -&gt; expect: no more key writes
-Lauterbach: session state = INACTIVE; read key buffer -&gt; expect: zeroed
-SIM sends tagged frames                             -&gt; expect: rejected
-trigger a new attempt (reset)                       -&gt; expect: authentication starts again
-Decision: OPEN
----</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
     </row>
     <row r="22" ht="240" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -2354,17 +4152,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MVC-103036</t>
+          <t>MVC-103033</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>New session after triggers</t>
+          <t>Calculate frame CMAC</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2.2.1.1.3-9</t>
+          <t>2.2.1.1.4-3</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2379,54 +4177,51 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The system shall require establishment of a new secure session, including full SOW1 authentication and generation of a new session key (SSK), after session expiry, system reset, system restart, session termination, or detection of a security failure.</t>
+          <t>The system shall calculate a 128-bit AES-CMAC tag over the selected rows of each video frame using the active 256-bit session key.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>MVC-106573. Test: CS-SOW1-018.</t>
+          <t>MVC-106583. Test: CS-SOW1-020.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>• Session lifetime: what is the expiry time? No requirement defines it.
-• "Security failure": which events (one bad CMAC frame? ten? an I2C error?). SRS MVC-108158 says "video authentication failure requiring session recovery", which has no definition either.
-• "System reset" and "system restart": what is the difference?</t>
+          <t>exactly which bytes form the message: only the pixel and embedded data of the selected rows, or also the line headers/footers and CSI-2 packet bytes? Row numbering base? (Samsung note.)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>two of the five triggers cannot be tested without these definitions. This also conflicts with 119710 (reject the frame and continue, SRS MVC-108105): the line between "reject one frame" and "start a new session" is missing. Proposal: define a lifetime, a failure threshold (for example N bad frames within T seconds) and merge reset and restart.</t>
+          <t>two implementations could calculate different tags for the same frame. Add the exact message construction and a test vector from Samsung.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>each trigger can be tested alone, as the verification criteria already say. Old key must be rejected afterwards: the SIM keeps sending frames with the old key.</t>
+          <t>a reference calculation (PyRef) works only if the tester knows the SSK and the exact input. With the SIM it is possible. A known-answer test vector from Samsung would make it independent of the SIM.</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>renegotiating while the camera streams: what happens to the video during the new authentication? Interruption time is not limited.</t>
+          <t>AES-CMAC with a 256-bit key is standard (NIST SP 800-38B, AES-256). The requirement says "128-bit tag": full output, not truncated, should be stated. The interval rule in MVC-108741 (at least 10 or 30 rows) exists so the imager finishes one row before the next. The host side has no stated rule on how fast it must compute.</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>several requirements in one (five triggers). Consider one requirement per trigger group, or keep it and give each trigger its own test (the technical test does this).</t>
+          <t>it also says "selected rows", which are defined in four other requirements (103055 note, 106576, 108741, 106574). Better to give the row selection its own concept requirement and reference it here.</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>MVC-106573. SRS MVC-108156, 108158, 108151.</t>
+          <t>MVC-106583. SRS MVC-108122, 108121, 108118.</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>for trigger in [expiry, reset, restart, termination, security failure]:
-    establish session; SIM sends frames with SSK_old -&gt; accepted
-    fire the trigger
-    Saleae: new auth read + new key block     -&gt; expect: yes
-    SIM decrypts the new block: SSK_new != SSK_old
-    SIM sends frames with SSK_old             -&gt; expect: rejected
+          <t>TE-1190: capture a real frame (raw rows)
+PyRef:   tag_ref = AES256-CMAC(SSK, selected rows as defined)
+SIM:     send the frame with tag_ref  -&gt; expect: accepted
+modify 1 byte in a selected row, keep tag_ref -&gt; expect: rejected
+modify 1 byte in a NOT selected row, keep tag_ref -&gt; expect: accepted (shows the coverage limit, record it)
 Decision: OPEN
 ---</t>
         </is>
@@ -2436,9 +4231,9 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
     </row>
     <row r="23" ht="240" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -2446,17 +4241,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MVC-119714</t>
+          <t>MVC-113701</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>No commands before authentication</t>
+          <t>CMAC over each command</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2.2.1.1.5-1</t>
+          <t>2.2.1.1.5-2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2471,134 +4266,45 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The system shall not transmit SOW1 control commands before successful SOW1 device authentication.</t>
+          <t>The system shall calculate a 128-bit AES-CMAC over each SOW1 control command using the established 256-bit session key.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>MVC-109119 ("protected SOW1 control commands"). Test: CS-SOW1-027.</t>
+          <t>MVC-108740. Test: CS-SOW1-028.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>which commands are "control commands"? The imager has to be configured over I2C (for example the settings files in SOW1/Imager Settings/) and the authentication itself is I2C traffic. Which I2C writes are allowed before authentication?</t>
+          <t>does the imager verify a command tag at all? The Volvo spec section 11 does not describe it. SRS MVC-108160 adds the tag "only when protected control command verification is supported by SOW1". What are the command format and the CMAC input?</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>read literally, the requirement forbids the writes needed to start the camera. The technical text says "protected" commands, the SRS too. Proposal: list the protected commands, or list the allowed pre-authentication ones, and use the word "protected" at concept level.</t>
+          <t>if the imager does not check it, the tag adds nothing. Proposal: confirm support first. If supported, put the exact input in the requirement (command, counter, order). The SRS says the counter is included before the tag is calculated (MVC-108159), so the counter is covered. The concept does not say it.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Saleae can list all writes to the imager address. The pass criterion needs the list from the SIQ.</t>
+          <t>the tag can be checked with PyRef from a captured command and the SSK. Whether the imager accepts or rejects a command with a wrong tag cannot be tested if the imager does not check.</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>the Volvo spec does not mention any protected command channel. See entry 23.</t>
+          <t>the concept says "each command", the SRS says "protected command only when supported". Conflict.</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>concept says "SOW1 control commands", technical says "protected SOW1 control commands": two terms.</t>
+          <t>113701 (calculate), 119707 (append), 113702 (counter) are three steps of one function. Proposal: one requirement for the protected command format: command + counter + CMAC.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MVC-109119. SRS MVC-108169.</t>
+          <t>MVC-108740. SRS MVC-108160, 108159.</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>reset; SIM does not complete authentication
-trigger a protected command (command source to confirm)
-Saleae: list all I2C writes to the imager          -&gt; expect: only the allowed pre-auth writes, no protected command
-repeat after authentication failure and before the key block was acknowledged
-complete authentication + session; trigger again    -&gt; expect: command sent
-Decision: OPEN
----</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24" ht="240" customHeight="1">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>MVC-113701</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>CMAC over each command</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1.1.5-2</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>CAL 2</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>The system shall calculate a 128-bit AES-CMAC over each SOW1 control command using the established 256-bit session key.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>MVC-108740. Test: CS-SOW1-028.</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>does the imager verify a command tag at all? The Volvo spec section 11 does not describe it. SRS MVC-108160 adds the tag "only when protected control command verification is supported by SOW1". What are the command format and the CMAC input?</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>if the imager does not check it, the tag adds nothing. Proposal: confirm support first. If supported, put the exact input in the requirement (command, counter, order). The SRS says the counter is included before the tag is calculated (MVC-108159), so the counter is covered. The concept does not say it.</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>the tag can be checked with PyRef from a captured command and the SSK. Whether the imager accepts or rejects a command with a wrong tag cannot be tested if the imager does not check.</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>the concept says "each command", the SRS says "protected command only when supported". Conflict.</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>113701 (calculate), 119707 (append), 113702 (counter) are three steps of one function. Proposal: one requirement for the protected command format: command + counter + CMAC.</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>MVC-108740. SRS MVC-108160, 108159.</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>trigger a protected command (to confirm)
 Saleae: capture the I2C write to the imager   -&gt; parse: cmd | counter | tag
@@ -2609,14 +4315,104 @@
 ---</t>
         </is>
       </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="240" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>MVC-107642</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Authenticate imager</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1.1.2-1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>CAL 2</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>The system shall authenticate the Imager by verifying the digital signature received from the Imager over the I2C interface using the provisioned Samsung Root Public Key.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>MVC-106561, 106565, 106563. Tests: CS-SOW1-002, 003, 004.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>• SIQ-1 (Samsung): define Device_n, KID, Sig_device. The Volvo spec says the signature covers "the device specific RSA public key along with the Device ID". The technical requirement says "over Device_n and KID". Is Device_n the key modulus and KID the Device ID? And is KID a key or algorithm identifier? The SRS (MVC-108135, 108136) lets KID select the signature scheme and hash.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>if the signed message is not defined byte for byte, SOW2 and the test cannot agree. Add the exact signed message and encoding to the technical requirement.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>needs signed data from the test root key. Negative cases (one field changed, other key) need the SIM.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>• The signature in the imager is a fixed value, stored in OTP and read over I2C. I found no challenge-response in the Volvo flow. A fake camera can copy the genuine data (it is not secret) and pass step 2. What stops it is that it does not hold the private key, so it cannot decrypt the session key and cannot produce a valid CMAC. Until the first valid tagged frame (frame 18 or later) SOW2 has no proof that the camera owns the key. Please confirm this is understood and accepted.
+• The concept fixes the scheme (107641), while the SRS makes KID select the scheme. See entry 10.</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>the concept requirement is verified by three technical requirements (request, verify, scheme). That is fine, but the pass criteria overlap. Keep each test about one thing.</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>concept to technical: three links. SRS 23.2.2 and 23.2.3 (MVC-108133, 108131, 108126, 108124, 108113, 108111).</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>SIM: serve genuine data (Device_n, KID, Sig_device signed by test root)
+Saleae: capture auth read           -&gt; expect: SOW2 asks for the fields; then accepts; key block follows
+SIM: flip 1 bit in Device_n / KID / Sig_device (one run each) -&gt; expect: rejected, no key block sent
+SIM: signature from another key     -&gt; expect: rejected
+SIM: copy genuine data, no private key (replay) -&gt; expect: auth accepted, but no valid CMAC frame ever -&gt; frames rejected
+Decision: OPEN
+---</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
     </row>
     <row r="25" ht="240" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -2701,9 +4497,9 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
     </row>
     <row r="26" ht="240" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -2711,17 +4507,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MVC-113702</t>
+          <t>MVC-103040</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Command counter</t>
+          <t>Extract device public key</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2.2.1.1.5-4</t>
+          <t>2.2.1.1.3-1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2736,50 +4532,51 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The system shall include a monotonically increasing Counter in each SOW1 control command transmitted.</t>
+          <t>Following successful authentication, The system shall extract 2048-bit device public key from the Imager's authentication data.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>MVC-109121. Test: CS-SOW1-030.</t>
+          <t>MVC-106577. Test: CS-SOW1-012.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>counter width, start value, behaviour at the maximum, and does the imager check it?</t>
+          <t>format of the key in the data (modulus only, fixed exponent?).</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>"monotonically" allows equal values. Proposal: "strictly increasing" and no reuse within the session (SRS MVC-108161). The counter restarts with each session because the key changes: say so. State the wrap rule (new session before wrap).</t>
+          <t>add sanity checks (length 2048 bits, odd modulus, exponent as defined) before the key is used.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>with Saleae the counter can be read from many commands. The maximum value case needs a test hook to preset the counter.</t>
+          <t>the extracted key is internal. Indirect check: SOW2 encrypts with it, and the SIM decrypts with its private key. If decryption works, the right key was used. Wrong-size or malformed keys signed with the test root key are easy to create.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>replay protection exists only if the imager rejects old counters. If it does not check, the counter protects nothing. Same open point as 113701.</t>
+          <t>the key is covered by the signature only if Device_n is the key modulus (SIQ in entry 9). If it is not covered, a key swap is possible.</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>see 113701.</t>
+          <t>NONE.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>MVC-109121. SRS MVC-108159, 108161.</t>
+          <t>MVC-106577. SRS 23.2.4.4 (MVC-108153) uses "the authenticated SOW1 Device public key".</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>send 100 protected commands; Saleae: read counter of each -&gt; expect: strictly increasing, no repeats
-reset (new session)                                      -&gt; counter restarts as defined
-Lauterbach: preset counter near the max; send commands   -&gt; expect: defined behaviour (new session before wrap)
-if the imager checks: replay an old command (old counter) -&gt; expect: rejected
+          <t>SIM: device key K1, signed by test root; authentication OK
+SIM: decrypt the key block that SOW2 writes with K1_priv  -&gt; expect: success (proves K1 was used)
+SIM: key of 1024 or 4096 bits, valid signature             -&gt; expect: rejected, no key block sent
+SIM: truncated or all-zero key, valid signature            -&gt; expect: rejected
+Lauterbach (optional): compare the key buffer with K1
 Decision: OPEN
 ---</t>
         </is>
@@ -2789,9 +4586,9 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S26"/>
@@ -2804,7 +4601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/CS-Testing/06-Requirements-Review/SOW1-SOW2_Review_Log.xlsx
+++ b/CS-Testing/06-Requirements-Review/SOW1-SOW2_Review_Log.xlsx
@@ -469,17 +469,17 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -576,46 +576,38 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• Frames 1-17 carry no tag: drop, accept or show?
-• Which rows does the CMAC cover?</t>
+          <t>Frames 1-17 have no tag: how to treat?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>• Text says 'each frame'; imager tags only frames 18+ and only selected rows.
-• Reword: 'each frame that carries a tag, over the selected rows'. Add a requirement for untagged frames.</t>
+          <t>Says 'each frame'; only frames 18+ are tagged. Reword.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>• Comparison is internal; same observable as 119710. Use the log event or a drop counter.
-• SIM needed: tester must know the session key.</t>
+          <t>Not observable alone; same as 119710.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>• Unselected rows and statistics are not authenticated.
-• No latency limit for holding a frame until verified.</t>
+          <t>Only selected rows are authenticated.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>• Merge with 119710, or split compare (119709) from reaction (119710).
-• TCR 106582 copies the text: add algorithm and input.</t>
+          <t>Merge with 119710.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106582 (ok).
-• Upstream MVC-106231 is too generic.
-• SRS 108112/108117/108122: link missing.</t>
+          <t>MVC-106582. SRS link missing.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>SIM: correct tag -&gt; frame accepted (RTP seen)
-SIM: flip 1 tag bit / truncate / wrong key / zero tag -&gt; rejected
-UART log: 'CMAC failed'</t>
+          <t>SIM sends good tag -&gt; accepted
+SIM flips 1 tag bit -&gt; rejected, log</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -647,42 +639,38 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>• PSS salt length and MGF?
-• Does KID select the scheme (SRS 108135)?</t>
+          <t>PSS salt length? Does KID select the scheme?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>• If only PSS/SHA-256 exists, drop the KID selection in the SRS; otherwise list accepted KIDs.</t>
+          <t>Define salt and MGF; align SRS on KID.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>• Partly inspection.
-• PKCS#1 v1.5 or another hash must fail; salt cases need the salt defined.</t>
+          <t>Partly inspection; salt untestable until defined.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>• Salt length, MGF and exponent are not stated.</t>
+          <t>Salt, MGF, exponent not stated.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>• Property of the 107642 verification: merge or keep as technical detail.</t>
+          <t>Merge into 107642.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>• MVC-106563 does not link back: add the link.
-• SRS 108120, 108135, 108136.</t>
+          <t>MVC-106563 not linked back.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Review: verify call = RSASSA-PSS + SHA-256
-PyRef: PSS/SHA-256 -&gt; accepted
-PKCS#1 v1.5, SHA-1, SHA-384 -&gt; rejected</t>
+          <t>Code review: PSS + SHA-256
+PyRef: v1.5 or SHA-1 signature -&gt; rejected</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -693,7 +681,7 @@
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
     </row>
-    <row r="4" ht="66" customHeight="1">
+    <row r="4" ht="54" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -714,44 +702,38 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>• Which DRBG and TRNG interface?
-• Evidence for SP 800-90A and TRNG quality (Ambarella)?</t>
+          <t>Which DRBG and TRNG? Compliance evidence?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>• Conformity is a design property: change the method to Review.
-• Keep a test for the failure behaviour.</t>
+          <t>Change method to Review.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>• Black-box shows only uniqueness.
-• Inject a TRNG error with Lauterbach.</t>
+          <t>Black-box shows only uniqueness.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>• SP 800-90A covers the DRBG, not the entropy source (800-90B).
-• No reseed rule.</t>
+          <t>No reseed rule.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>• Same TRNG as debug requirement MVC-103050.</t>
+          <t>Same TRNG as MVC-103050.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106560.
-• SRS 108106, 108109, 23.1.1.2.</t>
+          <t>MVC-106560.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Review: DRBG type and TRNG seed call; collect evidence
-Lauterbach: force TRNG error -&gt; no key block (Saleae)
-Collect 1000 SSKs via SIM -&gt; no repeats</t>
+          <t>Review DRBG + TRNG evidence
+Lauterbach: force TRNG error -&gt; no key sent</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -783,22 +765,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>• How does SOW2 know the imager accepted the key block?</t>
+          <t>How does SOW2 know the key was accepted?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>• 'Session established' is undefined; 119708, 103046, 103044 depend on it.</t>
+          <t>'Session established' is undefined.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>• Capture the write with Saleae; layout from the Samsung note.</t>
+          <t>Saleae capture; layout needed.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>• I2C CRC is ON (Volvo spec); a 256-byte block may need several writes: partial writes undefined.</t>
+          <t>Block may need several I2C writes.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -808,15 +790,13 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106578.
-• SRS 108146, 108145.</t>
+          <t>MVC-106578.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Saleae: after auth OK, write to imager key register = encrypted block, right length
-Order: auth read -&gt; verify -&gt; key write
-SIM acks -&gt; SESSION_ACTIVE; silent -&gt; not active</t>
+          <t>Saleae: key write only after auth OK
+SIM no ack -&gt; no session</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -848,44 +828,38 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>• After termination: no video, retry later, or safe state?
-• When is the next attempt allowed?</t>
+          <t>Reaction after termination: no video or safe state?</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>• A cybersecurity failure can switch off the camera image.
-• Define the reaction with FuSa.</t>
+          <t>Can switch off the camera image. Define reaction.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>• End state is observable (state, bus, stream).
-• 'No retry forever' needs a defined observation time.</t>
+          <t>End state is observable.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>• Concept says 'configured maximum', technical says a fixed three.</t>
+          <t>'Configured' vs fixed three.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>• See 103053.</t>
+          <t>See 103053.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106569.
-• SRS 108124 is similar.</t>
+          <t>MVC-106569.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>SIM never gives valid data; reset
-Saleae: no auth request or key write for 60 s
-Lauterbach: state UNAUTHENTICATED; valid-tag frames rejected
-Power cycle -&gt; new attempt</t>
+          <t>SIM never answers -&gt; Saleae: no more requests
+Lauterbach: state UNAUTHENTICATED</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -917,22 +891,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>• Reaction after termination: no video, new auth, or safe state?</t>
+          <t>Reaction after termination?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>• Define the next step and whether retries restart after a new authentication.</t>
+          <t>Define the next step.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>• End state is observable: no session, no more writes, key unused.</t>
+          <t>End state is observable.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>• The failed attempt's SSK must be erased (SRS 108149): check the buffer.</t>
+          <t>Erase the failed attempt's SSK.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -942,16 +916,13 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106581.
-• SRS 108149, 108158.</t>
+          <t>MVC-106581.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>SIM never acks the key block
-Saleae: no key writes for 60 s after last retry
-Lauterbach: state INACTIVE, key buffer zero
-Tagged frames rejected; reset -&gt; new attempt</t>
+          <t>SIM never acks -&gt; no more key writes
+Lauterbach: key buffer zero</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -962,7 +933,7 @@
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
     </row>
-    <row r="8" ht="78" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -983,44 +954,38 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>• Which OTP zone, and who programs it and when?</t>
+          <t>Which OTP zone? Who programs it?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>• Add 'prevent modification, replacement, deletion' (only in the verification text today).
-• Name the zone.</t>
+          <t>Add 'no modification'.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>• OTP is write-once: the overwrite test destroys a sample.
-• Test samples need a test root key.</t>
+          <t>Write-once: overwrite test destroys a sample.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>• Concept says OTP, SRS 108143 says 'protected non-volatile storage'.
-• Check free OTP size.</t>
+          <t>OTP vs 'protected NV storage' (SRS).</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>• Technical requirement copies the concept text.</t>
+          <t>TCR copies the text.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106562.
-• SRS 108143, 108142, 108144.
-• Secure-boot key (SRS 23.4) is a separate root.</t>
+          <t>MVC-106562. SRS 108143.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Lauterbach: read OTP zone; SHA-256(key) = Samsung fingerprint
-Try to write the zone -&gt; rejected; power cycle -&gt; unchanged
-SIM signs with test root -&gt; auth passes; other key -&gt; fails</t>
+          <t>Lauterbach: read OTP, compare hash
+Try write -&gt; rejected</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1052,43 +1017,38 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>• 3 retries (4 requests) or 3 attempts (3 requests)?
-• Timeout per attempt?</t>
+          <t>3 retries or 3 attempts? Timeout?</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>• Request count cannot be tested without one number.
-• Define N attempts in total and timeout T.</t>
+          <t>One number needed.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>• Count requests with Saleae; SIM withholds the answer.
-• Timing untestable until T is defined.</t>
+          <t>Count requests with Saleae.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>• 'Not received' vs invalid data: is a bad signature retried?</t>
+          <t>Bad signature: retry or reject?</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>• Retry rule is split over 103053 and 103051 with different wording.</t>
+          <t>Split with 103051.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106566.
-• SRS 108124, 108126.</t>
+          <t>MVC-106566.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>SIM: no answer to the auth read; reset
-Saleae: count auth requests until SOW2 stops = N
-SIM answers on request 2 -&gt; authentication continues</t>
+          <t>SIM silent -&gt; Saleae counts requests
+SIM answers on 2nd -&gt; continues</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1120,19 +1080,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>• What is the 'expected response', and the timeout per try?
-• Same block or new SSK on retry?</t>
+          <t>What is the 'expected response'? Timeout?</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>• Define the response, the timeout and what is resent.</t>
+          <t>Define response and timeout.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>• Count with Saleae; SIM withholds the response.
-• Blocked until the response is defined.</t>
+          <t>Blocked until response is defined.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1147,15 +1105,13 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106567.
-• SRS 108149.</t>
+          <t>MVC-106567.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>SIM accepts auth, ignores the key block
-Saleae: key writes = 1 + 3 (as decided)
-SIM answers on the 2nd -&gt; session established</t>
+          <t>SIM ignores key block -&gt; Saleae counts writes
+SIM answers on 2nd -&gt; session up</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1166,7 +1122,7 @@
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
     </row>
-    <row r="11" ht="78" customHeight="1">
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1187,43 +1143,38 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>• Session lifetime?
-• Which events are a 'security failure'?
-• Reset vs restart?</t>
+          <t>Session lifetime? What is a 'security failure'?</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>• 2 of 5 triggers are untestable; conflicts with 'reject one frame and continue'.
-• Define lifetime and failure threshold; merge reset and restart.</t>
+          <t>2 of 5 triggers untestable.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>• Each trigger is testable alone; SIM replays the old key afterwards.</t>
+          <t>Each trigger testable alone.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>• Video interruption during renegotiation is not limited.</t>
+          <t>Video gap during renegotiation not limited.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>• Five triggers in one requirement: test each separately.</t>
+          <t>Five triggers in one requirement.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106573.
-• SRS 108156, 108158, 108151.</t>
+          <t>MVC-106573.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>For each trigger (expiry, reset, restart, termination, failure): establish session, fire trigger
-Saleae: new auth + new key block; SIM: SSK_new != SSK_old
-Frames with SSK_old -&gt; rejected</t>
+          <t>Per trigger: new auth + new key (Saleae)
+Old-key frames -&gt; rejected</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1234,7 +1185,7 @@
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
     </row>
-    <row r="12" ht="78" customHeight="1">
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1255,24 +1206,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>• Counter wrap and first-frame value after a new session?</t>
+          <t>Counter wrap and first-frame value?</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>• More than 3 lost frames blocks every later valid frame until a new session.
-• Define a recovery.</t>
+          <t>More than 3 lost frames freezes video. Add recovery.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>• Boundaries are easy (=, &lt;, +1 to +4).
-• Wrap and first frame untestable until defined.</t>
+          <t>Boundaries easy; wrap undefined.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>• Update LastAcceptedCounter only after the CMAC passes: state the order.</t>
+          <t>Update counter only after CMAC passes.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1282,16 +1231,13 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-113727.
-• SRS 108099, 108104, 108102.
-• Recovery is in no requirement.</t>
+          <t>MVC-113727. Recovery missing.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>SIM (valid CMAC): n; n again -&gt; reject; n-1 -&gt; reject; n+1, n+3 -&gt; accept; n+4 -&gt; reject
-Forged high counter + wrong tag -&gt; rejected, LastAccepted unchanged (Lauterbach)
-Skip 5 frames -&gt; observe recovery</t>
+          <t>SIM: n+1, n+3 accepted; duplicate, n+4 rejected
+Forged counter -&gt; rejected</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1302,7 +1248,7 @@
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1323,42 +1269,38 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>• What does 'reject' do: drop, repeat previous frame, flag?</t>
+          <t>What does 'reject' do?</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>• Reaction undefined on a display camera.
-• Define: drop, count, log, continue (SRS 108105).</t>
+          <t>Define reaction: drop, log, continue.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>• Same observable as 119709: define log or counter.</t>
+          <t>Same observable as 119709.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>• No threshold for repeated bad frames.
-• Random corruption and forgery get the same reaction?</t>
+          <t>No limit for repeated bad frames.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>• Overlaps 119709 and SRS 108116.</t>
+          <t>Overlaps 119709.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106564 (ok).
-• SRS 108116, 108108, 108105.</t>
+          <t>MVC-106564.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>SIM: 10 good, 1 bad tag, 10 good
-Wireshark: bad frame missing from RTP
-Lauterbach: drop counter = 1</t>
+          <t>SIM sends 1 bad frame
+Wireshark: frame missing; log entry</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1369,7 +1311,7 @@
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
     </row>
-    <row r="14" ht="54" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1390,42 +1332,38 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>• Which commands are 'control commands'?
-• Which I2C writes are allowed before authentication?</t>
+          <t>Which commands are 'control commands'?</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>• Read literally, it forbids the writes needed to start the camera.
-• Use 'protected' and list the commands.</t>
+          <t>Literally blocks camera startup writes. List them.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>• Saleae lists all writes; the pass criterion needs the command list.</t>
+          <t>Needs the command list.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>• Volvo spec has no protected command channel.</t>
+          <t>Not in the Volvo spec.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>• Concept says 'control commands', technical says 'protected'.</t>
+          <t>'Control' vs 'protected'.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-109119.
-• SRS 108169.</t>
+          <t>MVC-109119.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Reset, auth blocked; trigger a protected command
-Saleae: only allowed pre-auth writes, no protected command
-After auth + session -&gt; command is sent</t>
+          <t>Auth blocked -&gt; Saleae: no protected writes
+Auth OK -&gt; command sent</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1436,7 +1374,7 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
     </row>
-    <row r="15" ht="66" customHeight="1">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1458,37 +1396,33 @@
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>• 'Any accessible interface' needs a list: UART, JTAG, logs, SOME/IP/DTLS diagnostics, dumps, I2C, flash.</t>
+          <t>List the 'accessible interfaces'.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>• Negative test: needs the interface list and the SSK (from SIM).</t>
+          <t>Negative test; needs SSK from SIM.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>• SSK is in DRAM; authorised debug can read it.
-• Exclude the key region or accept an exception.</t>
+          <t>Authorised debug can read SSK in DRAM.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>• Technical requirement copies the text; SRS has 4 related requirements.</t>
+          <t>TCR copies the text.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106571.
-• SRS 108164, 108163, 108154, 108157; debug and DRAM requirements.</t>
+          <t>MVC-106571.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>SIM: get SSK; JTAG locked -&gt; Lauterbach denied
-Search I2C, Ethernet, UART captures for SSK bytes -&gt; none
-Trigger failures, read logs -&gt; no key
-Unlocked debug: read DRAM key region -&gt; record</t>
+          <t>Search all captures for SSK bytes
+JTAG locked -&gt; denied</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1520,23 +1454,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>• What happens to 'untrusted' video: dropped or passed with a flag? (safety decision)</t>
+          <t>'Untrusted' video: drop or flag?</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>• Two very different implementations are possible.
-• Define the reaction and who evaluates it.</t>
+          <t>Define the reaction.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>• Observable only on the outgoing RTP stream or a status signal.</t>
+          <t>Observe the outgoing RTP stream.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>• 'Session established' is not defined (see 103034).</t>
+          <t>'Session established' undefined.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1546,16 +1479,13 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-109120.
-• SRS 108138.
-• Reaction is in no requirement.</t>
+          <t>MVC-109120.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Reset; SIM silent on authentication
-SIM sends frames -&gt; Wireshark: no trusted video
-Repeat after auth failure and after session end; after auth + session -&gt; video flows</t>
+          <t>Auth blocked -&gt; Wireshark: no trusted video
+Auth OK -&gt; video flows</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1566,7 +1496,7 @@
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
     </row>
-    <row r="17" ht="66" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1587,44 +1517,38 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>• Counter width, start value, max behaviour?
-• Does the imager check it?</t>
+          <t>Counter width, start, wrap? Imager checks it?</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>• 'Monotonic' allows equal values: use 'strictly increasing, no reuse in a session' (SRS 108161).
-• State the wrap rule.</t>
+          <t>Use 'strictly increasing'.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>• Read counters with Saleae.
-• Max case needs a preset hook.</t>
+          <t>Read counters with Saleae.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>• Replay protection exists only if the imager rejects old counters.</t>
+          <t>Useless if imager ignores the counter.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>• See 113701.</t>
+          <t>See 113701.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-109121.
-• SRS 108159, 108161.</t>
+          <t>MVC-109121.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Send 100 commands; Saleae: strictly increasing
-Reset -&gt; counter restarts as defined
-Lauterbach: preset near max -&gt; new session before wrap
-If imager checks: replay old command -&gt; rejected</t>
+          <t>100 commands -&gt; counters strictly increase
+Replay old command -&gt; rejected</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1657,13 +1581,12 @@
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>• 'New key every session' is only in the verification text: add it (SRS 108110).</t>
+          <t>Add 'new key every session'.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>• SSK is visible only through the SIM.
-• Randomness cannot be proven, only repeats.</t>
+          <t>SSK visible only via SIM.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1673,21 +1596,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>• Overlaps 103042 (how) and 103036 (new each session).
-• Keep length + new-each-session here.</t>
+          <t>Overlaps 103042 and 103036.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106568.
-• SRS 108107, 108110.</t>
+          <t>MVC-106568.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Loop 1000: reset, authenticate, SIM decrypts key block, store SSK
-Check: 32 bytes, no duplicates
-Auth failure -&gt; no key block on I2C</t>
+          <t>1000 sessions via SIM -&gt; 32 bytes, no repeats</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1698,7 +1617,7 @@
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
     </row>
-    <row r="19" ht="54" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1719,41 +1638,38 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>• Counter width, start value, wrap, reset per stream?</t>
+          <t>Counter width, wrap, start value?</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>• Window rule cannot be checked at wrap without the width.</t>
+          <t>Width needed for the window rule.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>• Read the counter with Lauterbach.
-• SIM sends boundary values.</t>
+          <t>Read with Lauterbach.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>• Counter is protected only if the header row is inside the CMAC rows (start row 0).</t>
+          <t>Protected only if header row is in CMAC.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>• 'Use for freshness' duplicates 113703 / MVC-106575: keep extraction only.</t>
+          <t>'Use' duplicates 113703.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-113726 and MVC-106575.
-• SRS 108099.</t>
+          <t>MVC-113726, 106575.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>SIM: counters 1..N
-Lauterbach: extracted counter = sent value
-SIM: counter at max, then 0 -&gt; defined wrap; missing header -&gt; rejected</t>
+          <t>SIM counters 1..N -&gt; Lauterbach matches
+Missing header -&gt; rejected</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1764,7 +1680,7 @@
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -1785,41 +1701,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>• Footer position, length, byte order? (Samsung note missing)</t>
+          <t>Footer layout and byte order?</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>• Layout needed to implement and test.
-• Add the layout reference to the technical requirement.</t>
+          <t>Layout needed to implement and test.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>• Internal step: read the buffer with Lauterbach or infer from acceptance.</t>
+          <t>Read buffer with Lauterbach.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>• Footer is absent in frames 1-17.</t>
+          <t>No footer in frames 1-17.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>• Implementation step of 119709: keep at technical level or merge.</t>
+          <t>Step of 119709.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106572.
-• SRS 108140, 108129, 108134, 108132.</t>
+          <t>MVC-106572.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>SIM: frame with known tag T
-Lauterbach: extracted tag = T (10 different tags)
-SIM: missing or short footer -&gt; rejected, no crash</t>
+          <t>SIM sends known tag T
+Lauterbach: extracted = T
+Short footer -&gt; rejected</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1830,7 +1744,7 @@
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
     </row>
-    <row r="21" ht="78" customHeight="1">
+    <row r="21" ht="90" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -1851,43 +1765,38 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>• Message layout (SSK, Row_info_00/01), OAEP label, MGF1 hash? (Samsung note missing)</t>
+          <t>Message layout, OAEP label, MGF1?</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>• Layout is needed by implementation and test: put it in the technical requirement.</t>
+          <t>Put layout in the technical requirement.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>• OAEP is randomised: compare plaintexts only.
-• Known SSK needs a test hook.</t>
+          <t>OAEP is random: compare plaintext only.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>• RSA-2048 OAEP/SHA-256 holds max 190 bytes: 32-byte SSK + Row_info fits.
-• Row rules depend on the output mode.</t>
+          <t>OAEP limit 190 bytes: SSK + Row_info fits.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>• 4 technical requirements, 3 about row selection: give row selection its own concept requirement.</t>
+          <t>Row rules need own requirement.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106580, 106576, 108741, 106574.
-• SRS 108153, 108145, 108165, 108166.</t>
+          <t>MVC-106580, 106576, 108741, 106574.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>SIM: decrypt key block (OAEP, SHA-256) -&gt; SSK + Row_info
-Lauterbach: Row_info used = decrypted
-Wrong private key -&gt; fails; no SSK in plaintext on I2C
-Bad row settings -&gt; refused</t>
+          <t>SIM decrypts key block -&gt; SSK + Row_info
+Wrong key -&gt; fails</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1919,43 +1828,38 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>• Exact CMAC input bytes: pixel data only, or line headers too?
-• Row numbering base?</t>
+          <t>Exact CMAC input bytes?</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>• Two implementations could produce different tags.
-• Add exact input and a Samsung test vector.</t>
+          <t>Add exact input + test vector.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>• Reference calculation needs the SSK and exact input: SIM only.</t>
+          <t>Needs SSK: SIM only.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>• AES-256 CMAC, full 128-bit tag: state 'not truncated'.
-• No host-side speed requirement.</t>
+          <t>State full 128-bit tag.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>• Row selection is defined in 4 other requirements: give it its own concept requirement.</t>
+          <t>Row selection needs own requirement.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106583.
-• SRS 108122, 108121, 108118.</t>
+          <t>MVC-106583.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>TE-1190: capture frame rows
-PyRef: tag = AES256-CMAC(SSK, selected rows)
-SIM: send -&gt; accepted; change 1 byte in a selected row -&gt; rejected; in an unselected row -&gt; accepted</t>
+          <t>PyRef tag -&gt; SIM sends -&gt; accepted
+Change selected byte -&gt; rejected</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1966,7 +1870,7 @@
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
     </row>
-    <row r="23" ht="54" customHeight="1">
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -1987,44 +1891,38 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>• Does the imager verify command tags at all?
-• Command format and CMAC input?</t>
+          <t>Does the imager check command tags?</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>• If the imager does not check, the tag adds nothing: confirm first.
-• Then fix the input (command + counter, SRS 108159).</t>
+          <t>Confirm support; fix CMAC input.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>• Tag checkable with PyRef.
-• Imager rejection untestable if it does not check.</t>
+          <t>Imager rejection untestable if unchecked.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>• Concept: 'each command'. SRS: 'only when supported by SOW1'. Conflict.</t>
+          <t>Concept 'each'; SRS 'only if supported'.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>• 113701, 119707, 113702 are steps of one function: merge into one 'protected command format'.</t>
+          <t>Merge with 119707, 113702.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-108740.
-• SRS 108160, 108159.</t>
+          <t>MVC-108740.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Trigger a protected command
-Saleae: parse cmd | counter | tag
-PyRef: AES256-CMAC(SSK, cmd||counter) = tag
-If imager checks: wrong tag -&gt; rejected</t>
+          <t>Saleae: parse cmd | counter | tag
+PyRef recomputes tag -&gt; equal</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2035,7 +1933,7 @@
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
     </row>
-    <row r="24" ht="78" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -2056,43 +1954,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>• Define Device_n, KID, Sig_device and the exact signed message (Volvo spec: key + Device ID).</t>
+          <t>Define Device_n, KID, signed message.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>• Signed message must be defined byte for byte, or SOW2 and test disagree.</t>
+          <t>Signed data must be byte-exact.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>• Needs signatures from a test root key.
-• Negative cases need the SIM.</t>
+          <t>Needs test root key + SIM.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>• Signature is static (no challenge): a copied record passes this step.
-• Only the CMAC (frame 18+) proves the private key.
-• Concept fixes the scheme, SRS lets KID choose.</t>
+          <t>Static signature: a copied record passes.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>• Three technical requirements verify it: keep tests separate per topic.</t>
+          <t>Three technical requirements verify it.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106561/106565/106563.
-• SRS 108133, 108131, 108126, 108124, 108113, 108111.</t>
+          <t>MVC-106561, 106565, 106563.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>SIM serves genuine data -&gt; Saleae: key block follows
-Flip 1 bit in Device_n / KID / Sig -&gt; rejected, no key sent
-Replay genuine data without the private key -&gt; auth passes, frames rejected</t>
+          <t>SIM genuine -&gt; key block follows
+Flip 1 bit -&gt; rejected
+Replayed copy -&gt; no valid frames</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2103,7 +1997,7 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
     </row>
-    <row r="25" ht="54" customHeight="1">
+    <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -2124,41 +2018,38 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>• Field order and size in the I2C write?
-• Where does the I2C CRC go?</t>
+          <t>Field order? Position of I2C CRC?</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>• Define the layout in the technical requirement, with an example.</t>
+          <t>Define layout with an example.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>• Easy with Saleae once the layout is defined.</t>
+          <t>Easy with Saleae.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>• If CMAC generation fails, no command may be sent (SRS 108160): add it.</t>
+          <t>No command if CMAC fails.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>• See 113701.</t>
+          <t>See 113701.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106570.
-• SRS 108160.</t>
+          <t>MVC-106570.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Saleae: write = [cmd][counter][16-byte tag] in the defined order
-Lauterbach: force CMAC failure -&gt; nothing sent
-Repeat for 3 commands</t>
+          <t>Saleae: [cmd][counter][tag]
+Force CMAC failure -&gt; nothing sent</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2169,7 +2060,7 @@
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
     </row>
-    <row r="26" ht="66" customHeight="1">
+    <row r="26" ht="54" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -2190,22 +2081,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>• Key format: modulus only? Fixed exponent?</t>
+          <t>Key format and exponent?</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>• Add sanity checks (2048 bit, odd modulus, exponent) before use.</t>
+          <t>Add key sanity checks.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>• Internal: check indirectly. SIM decrypts the key block with its private key.</t>
+          <t>SIM decrypt proves the right key.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>• Key is covered by the signature only if Device_n is the modulus.</t>
+          <t>Signature must cover the key.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2215,15 +2106,13 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>• Linked to MVC-106577.
-• SRS 108153.</t>
+          <t>MVC-106577.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>SIM: decrypt SOW2's key block with K1 private -&gt; success
-SIM key of 1024 or 4096 bits, valid signature -&gt; rejected
-Truncated or zero key -&gt; rejected</t>
+          <t>SIM decrypts key block -&gt; ok
+Wrong-size key -&gt; rejected</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">

--- a/CS-Testing/06-Requirements-Review/SOW1-SOW2_Review_Log.xlsx
+++ b/CS-Testing/06-Requirements-Review/SOW1-SOW2_Review_Log.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Review!$A$1:$N$26</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Review!$A$1:$N$57</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Review (detailed)'!$A$1:$S$26</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="904">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -823,6 +823,901 @@
   <si>
     <t xml:space="preserve">SIM decrypts key block -&gt; ok
 Wrong-size key -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOW 1 - SOW 2 interface TECHNICAL requirements (TCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same open question as concept 119709: how are frames 1-17 (no tag) handled?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text copies concept 119709. Add the how: AES-CMAC, 256-bit key, 128-bit tag over the rows set by 106576, 108741, 106574, 106583.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criteria are good: valid tag, flipped footer tag, modified data, partial 128-bit match. Needs the SIM to know the session key.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'No partial match' is only in the criteria. Add 'all 128 bits' to the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical text to concept MVC-119709. Merge with 106564 (reject).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-119709. Test CS-SOW1-021.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM: valid tag -&gt; accepted
+Flip tag bit or change data -&gt; rejected
+Tag with only 64 bits right -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freshness, ordering, sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall verify the freshness, ordering, and sequence validity of each received SOW1 video frame using the frame counter embedded in the frame header.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the 'specified counter-validation policy'? It is defined only in 113727.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlaps 113727 (window rule). Reference 113727 here, or merge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criteria cover duplicate, stale, out-of-order and boundary frames: same tests as 113727.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A malformed or missing counter must never count as fresh (criterion 5). Add it to the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies 103031 (extraction) but describes the validity check. Move it under 113703.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103031. Test CS-SOW1-023. Overlaps MVC-113727.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM: increasing counters -&gt; accepted
+Duplicate, stale, out of order -&gt; rejected
+Missing counter -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall use RSASSA-PSS whith SHA-256 to verify the Imager's digital signature (Sig_device).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSS salt length and MGF? Is PSS with SHA-256 the only scheme (the SRS lets KID select)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define salt and MGF. Fix the typo 'whith' and the criteria numbering (step 3 is missing).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1 is an inspection. Wrong scheme or parameters must fail; salt cases are untestable until defined.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification detail of 106565. Merge or reference it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-107642 only. MVC-107641 is not linked: add it. Test CS-SOW1-004.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code review: PSS + SHA-256
+PyRef: PKCS#1 v1.5 or SHA-1 signature -&gt; rejected
+Modify signed data -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which DRBG and TRNG interface? Evidence for SP 800-90A?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same text as concept 103042. 'No insecure fallback' is only in the criteria: add it to the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steps 1-2 are a review. Steps 3-5 (inject a TRNG failure, no fallback) can be tested with Lauterbach.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE: no reseed rule, and 'approved seeding mechanism' is not defined.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 103042. Set the method to Review for the compliance part.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103042. Test CS-SOW1-011.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review DRBG + TRNG evidence
+Lauterbach: force TRNG error -&gt; no key, no I2C key write</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall transmit the encrypted session key and selected row information (Row_info) to SOW1 over the I2C interface.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are the message layout, length and field encoding? (Samsung note missing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The layout is called 'specified' but is not given. Add it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saleae on the I2C bus; compare the block with the SIM's decryption. No transmission if authentication or encryption fails (criterion 6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE: the block may need several I2C writes; partial-write handling is undefined.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row_info appears here and in 106580. Keep 'what is sent' here, 'how it is encrypted' there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103034. Test CS-SOW1-014.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saleae: key write only after auth OK, right length
+SIM decrypts block -&gt; SSK + Row_info
+Force encryption failure -&gt; no write</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall terminate the SOW1 authentication process if authentication is not successfully completed after three authentication attempts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three attempts here, 'configured maximum' in the concept. Which is right?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix one rule. 106566 says retransmit 3 times (4 requests), this says 3 attempts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End state is checkable: unauthenticated, no session, no endless retransmission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No time limit between attempts, so 'indefinitely' cannot be bounded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align the wording with 106566 (attempt vs retransmit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103051. Test CS-SOW1-006.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM never answers -&gt; Saleae: requests stop at the limit
+Lauterbach: state UNAUTHENTICATED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are the 'recovery conditions' in step 5?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define when a new establishment may start after termination.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End state is observable: not active, no more retries, key unused.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE: erase the SSK of the failed attempt (SRS 108149).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same text as concept 103044.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103044. Test CS-SOW1-017.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM never acks the key block -&gt; no key writes after 3 retries
+Lauterbach: state INACTIVE, key buffer zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which OTP/eFuse location? Why does step 4 mention the Secure Boot function?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criteria say the Secure Boot function reads this key, but the Samsung root and the secure-boot root are different. Fix the criteria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP is write-once: the immutability test destroys a sample. A test root key is needed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Immutable after provisioning' is only in the criteria. Add it to the text (SRS 108142).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same text as concept 103063.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103063. SRS 108143. Test CS-SOW1-001.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauterbach: read OTP location, hash = fingerprint
+Try write -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are the 'expected response' and the 'configured limit'?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define the response, the limit and the timeout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count key writes with Saleae while the SIM withholds the response.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same text as concept 103046.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103046. Test CS-SOW1-016.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM ignores the key block -&gt; Saleae counts writes
+SIM answers on the 2nd -&gt; session established</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retransmit authentication request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall retransmit the SOW1 authentication request up to three times if the expected authentication data is failed to be received.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Retransmit three times' means 4 requests. Is that intended?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contradicts 'three attempts' in 106569. One number is needed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 5 tests the last permitted attempt: a good boundary. Needs the SIM to answer late.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retry timing is missing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retry here, terminate in 106569: align the wording.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103053. Test CS-SOW1-005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM silent -&gt; Saleae counts requests
+SIM answers on the last allowed attempt -&gt; continues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session lifetime? What is a 'security failure'? Reset vs restart?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same gaps as concept 103036: two triggers are untestable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criteria test each trigger alone, including old SSK refused and no resume before the new session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 103036; five triggers in one requirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103036. Test CS-SOW1-018.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per trigger: new auth + new key
+Old-key frames -&gt; rejected
+No protected traffic before the new session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request authentication data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall request the SOW1 device authentication data, including Device_n, KID, and Sig_device, from SOW1 over the I2C interface after reset or before starting the secure session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the 'defined authentication error and retry behavior' (step 5)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is defined only in the retry requirements. Reference them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saleae on reset: request sent to the configured device with the three fields.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Before starting the secure session' needs a precise definition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request here, verification in 106565: fine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-107642. Test CS-SOW1-002.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset -&gt; Saleae: auth read request to the imager
+SIM incomplete answer -&gt; handled as missing data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-113727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter width, wrap and first-frame value?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More than 3 lost frames freeze the video. Add a recovery rule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very good boundary list (equal, lower, +1, +2, +3, +4). Wrap is untestable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE: 'update only after authentication' is in the criteria, not in the text. Add it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 113703.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-113703. Test CS-SOW1-026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM (valid CMAC): n+1, n+3 accepted; duplicate, n+4 rejected
+Forged counter + wrong tag -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What does 'rejected' do with the frame?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define: drop, count, log, continue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criteria cover bad tag and modified data; the frame must not be forwarded as trusted, nor accepted later by another path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE: no limit for repeated bad frames.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 119710. Merge with 106582.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-119710. Test CS-SOW1-022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List the 'accessible interfaces' in the text. The criteria already name diagnostics, logs, debug, communication and memory paths.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs the SSK from the SIM and captures on each interface. Step 5 needs a defined 'authorized boundary'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SSK sits in DRAM and authorised debug can read it. Exclude it or accept an exception.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 113706.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-113706. Test CS-SOW1-015.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search all captures for SSK bytes
+JTAG locked -&gt; denied
+Read logs after failures -&gt; no key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-109120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How is 'trusted' marked: dropped or flagged? (safety decision)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define the reaction for untrusted video.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criteria cover before authentication, after failure, after termination, and 'trusted processing' after a valid session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Trusted' also depends on integrity and freshness (step 5). Say so in the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 119708.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-119708. Test CS-SOW1-024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-109121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall include a monotonically increasing Counter in each protected SOW1 control command.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter width? What are the 'exhaustion/rollover policy' and 'initialization policy'?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both policies are in the criteria but defined nowhere. Define them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum case needs a way to preset the counter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Monotonically' allows equal values: use 'strictly increasing'. The imager must check it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Protected' command here, 'control command' in concept 113702.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-113702. Test CS-SOW1-030.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 commands -&gt; counters strictly increase
+Reset -&gt; counter restarts as defined
+Replay old command -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall generate a 256-bit cryptographically random session key (SSK) following successful authentication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'New key every session' is only in the criteria. Add it to the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SSK is visible only through the SIM. Check length and uniqueness over many sessions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overlaps 106560 (how) and 106573 (new each session).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103057. SRS 108110. Test CS-SOW1-010.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000 sessions via SIM -&gt; 32 bytes, no repeats
+Auth failure -&gt; no key block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-113726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter width and supported range?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define the counter range (step 4 refers to the 'supported counter range').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read the counter with Lauterbach. A malformed header must not authorise a frame.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The counter is authenticated only if the header row is in the CMAC rows (106576).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 103031. The freshness use is in 106575 and 113727.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103031. Test CS-SOW1-025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM counters 1..N -&gt; Lauterbach matches
+Missing or short header -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer position and byte order? (Samsung note missing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Defined footer field' is not defined. Add it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known tags in, extracted value compared. Malformed footers must not count as extracted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No footer tag in frames 1-17.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 113705. A step of 106582.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-113705. Test CS-SOW1-019.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected row range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall ensure that the selected row range does not exceed the total vertical data size, including the image data and embedded header and statistics data, according to the following constraint:
+start + 1 + (interval + 1) × (total − 1) ≤ ysize_image + ysize_embedded_data
+where start is the starting row, interval is the row interval, total is the number of selected rows, and ysize_image and ysize_embedded_data are the vertical sizes of the image and embedded data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is 'start' 0-based, and does 'total' include the header row?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define the indexing so the boundary test is unambiguous.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good boundary tests: exact fit accepted, one row more rejected, minimum values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE: use the real configured sizes and avoid integer overflow or truncation (criterion 5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row rules sit under concept 103055 (encrypt). Give row selection its own concept requirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103055. Test CS-SOW1-009.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure start/interval/total at the exact limit -&gt; accepted
+One row over -&gt; rejected or corrected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall encrypt the session key and selected row information (Row_info) using the 2048-bit device public key with RSAES-OAEP and SHA-256.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAEP label and MGF? Step 6 says to check them against the 'approved interface specification'. Which one?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name the specification (Samsung note) and put label and MGF in the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAEP is random, so compare plaintexts only. A known SSK needs a test hook.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSA-2048 with OAEP and SHA-256 holds at most 190 bytes, so SSK + Row_info fits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row_info appears here and in 106578. Keep the encryption here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103055. SRS 108153. Test CS-SOW1-013.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM decrypts key block (OAEP, SHA-256) -&gt; SSK + Row_info
+Wrong private key -&gt; fails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row start value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall configure the row start value of Row_info_00 or Row_info_01 to either 0 or 1 to include the embedded header containing the video frame counter in the AES-CMAC input.
+Note: If Row start value set as 0, first line will be included as a AES-CMAC input. - If Row start value set as 1, second line will be included as a AES-CMAC input.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the 'configuration-validation policy' for values other than 0 and 1?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Say 'rejected' instead of 'rejected or handled by policy'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check start 0 and 1, the encoding in Row_info, and invalid values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start 0 puts the header with the frame counter inside the CMAC, which authenticates the counter. State this reason in the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row rules: see 106574. Give them their own concept requirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103055. Test CS-SOW1-007.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure start 0 -&gt; header row in CMAC input
+Start 1 -&gt; second line
+Start 2 -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-108741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall configure the row interval to be at least 10 for Merge Compressed or Merged output mode (RAW12, RAW14, RAW16, RAW20, and RAW24), and at least 30 for Line Reorder mode (RAW12), to ensure that AES-CMAC calculation for the preceding selected row is completed before the next selected row is input for AES-CMAC calculation.
+Note: Row information format is defined by Samsung, which is described in ‘5 Key sharing’ chapter in S5K3B6SA - Cybersecurity Application note documnet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What interval applies to the other output modes? Step 4 says not 'an unrelated mode's minimum'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List every supported mode with its minimum interval.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 3 measures CMAC timing per row on the imager: needs a frame capture and a timing reference.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rule protects the imager's timing, not SOW2. State that SOW2 configures it and who enforces it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row rules: see 106574.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103055. Test CS-SOW1-008.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAW12 merged mode: interval &lt; 10 -&gt; refused
+Line reorder: interval &lt; 30 -&gt; refused
+Unsupported mode -&gt; no borrowed minimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall calculate a 128-bit AES-CMAC tag over the selected rows of each video frame using the active 256-bit AES session key.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exact CMAC input and the 'approved input encoding'?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add the exact input and a Samsung test vector.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference tag from PyRef with the SSK from the SIM. Criterion 6: not a fixed or old key.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE: state that the full 128-bit tag is used (no truncation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text says 'AES session key', the concept says 'session key'. Use one term.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103033. Test CS-SOW1-020.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PyRef tag -&gt; SIM sends frame -&gt; accepted
+Change a selected byte -&gt; rejected
+Previous-session key -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-108740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate command CMAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the 'command's specified authenticated input'? Does the imager check the tag?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define the input (command + counter, SRS 108159). Confirm imager support.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concept says 'each command', SRS says 'only if supported by SOW1'. Conflict.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 113701. Merge with 106570 and 109121.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-113701. Test CS-SOW1-028.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saleae: parse cmd | counter | tag
+PyRef recomputes tag -&gt; equal
+Previous-session key -&gt; tag differs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authenticate SOW1 signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system shall authenticate SOW1 by verifying Sig_device over Device_n and KID using the trusted RSA-2048 Samsung Root Public Key.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is Device_n the key modulus and KID the Device ID? The Volvo spec says the signature covers the device key plus Device ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define the signed message byte for byte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good negative cases: modified Device_n, modified KID, wrong signature, untrusted key. Needs a test root key and the SIM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The signature is static (no challenge), so a copied record passes this step.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-107642. Test CS-SOW1-003.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM genuine data -&gt; key block follows
+Flip 1 bit in Device_n or KID -&gt; rejected
+Untrusted key -&gt; rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Append command tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field order, encoding, and where does the I2C CRC go?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define the layout with an example.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saleae shows command followed by tag; different commands get different tags.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE: no command is sent as protected if CMAC calculation fails (criterion 6, SRS 108160). Add it to the text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 119707.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-119707. Test CS-SOW1-029.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saleae: [cmd][counter][16-byte tag] in order
+Force CMAC failure -&gt; not sent as protected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-109119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SOW2 shall not transmit protected SOW1 control commands before successful authentication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which commands are 'protected'?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List them. This text says 'The SOW2', the others say 'The system': use one subject.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saleae lists all writes to the imager. The allowed pre-authentication writes must be listed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 4 also needs the 'other secure-session requirements'. Name them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concept says 'control commands', this says 'protected'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-119714. Test CS-SOW1-027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auth blocked -&gt; Saleae: no protected writes
+Session ended -&gt; commands stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVC-106577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key format: modulus only? Exponent?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add sanity checks before use. Criterion 5 already says invalid keys must not be used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM decrypts the key block: success proves the right key was used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered by the signature only if Device_n is the modulus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to concept 103040.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfies MVC-103040. Test CS-SOW1-012.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM decrypts key block with its private key -&gt; ok
+Wrong-size or zero key -&gt; rejected</t>
   </si>
   <si>
     <t xml:space="preserve">Outline</t>
@@ -1769,7 +2664,7 @@
     <t xml:space="preserve">Without them the message layouts and the valid signatures cannot be produced</t>
   </si>
   <si>
-    <t xml:space="preserve">Summary of review comments: SOW1 - SOW2 interface concept</t>
+    <t xml:space="preserve">Summary of review comments: SOW1 - SOW2 interface (concept and technical requirements)</t>
   </si>
   <si>
     <t xml:space="preserve">'-' in the Review sheet means no comment. 'SWE:' marks a point that is not in the concept or technical (system) requirements and belongs to the software requirements (SRS).</t>
@@ -1778,7 +2673,13 @@
     <t xml:space="preserve">Count (formulas over the Review sheet)</t>
   </si>
   <si>
-    <t xml:space="preserve">Value</t>
+    <t xml:space="preserve">Concept (rows 2-26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical (rows 28-57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
   </si>
   <si>
     <t xml:space="preserve">Requirements reviewed</t>
@@ -1826,7 +2727,7 @@
     <t xml:space="preserve">1. Frames 1-17 have no tag</t>
   </si>
   <si>
-    <t xml:space="preserve">119709, 113705, 119708</t>
+    <t xml:space="preserve">119709, 113705, 119708 (TCR 106582, 106572, 109120)</t>
   </si>
   <si>
     <t xml:space="preserve">The imager sends no CMAC for the first 17 frames, but the requirements say "each frame". Define how those frames are treated.</t>
@@ -1838,22 +2739,25 @@
     <t xml:space="preserve">2. Reaction to a failure is undefined</t>
   </si>
   <si>
+    <t xml:space="preserve">119710, 119708, 103051, 103044 (TCR 106564, 109120, 106569, 106581)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reject, untrusted and terminate do not say what the ECU does with the video. A failure can switch off the camera image. Needs a safety decision.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Retry counts and timeouts</t>
   </si>
   <si>
-    <t xml:space="preserve">103053, 103051, 103046, 103044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Three retries" and "three attempts" mean different request counts. Timeouts and the meaning of "expected response" are missing. One number is needed.</t>
+    <t xml:space="preserve">103053, 103051, 103046, 103044 (TCR 106566, 106569, 106567, 106581)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Three retries" (4 requests) and "three attempts" (3 requests) differ. Concept says "configured maximum", TCR says a fixed three. Timeouts and "expected response" are missing.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Session definition</t>
   </si>
   <si>
-    <t xml:space="preserve">103034, 103036, 103046</t>
+    <t xml:space="preserve">103034, 103036, 103046 (TCR 106578, 106573, 106567)</t>
   </si>
   <si>
     <t xml:space="preserve">No requirement says when a session is established, how long it lives, or what a "security failure" is. Two of five new-session triggers cannot be tested.</t>
@@ -1862,10 +2766,10 @@
     <t xml:space="preserve">5. Freshness and counters</t>
   </si>
   <si>
-    <t xml:space="preserve">113703, 103031, 113702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 3-frame window freezes the video after more than 3 lost frames. Counter width, wrap, start value and check order are not defined.</t>
+    <t xml:space="preserve">113703, 103031, 113702 (TCR 113727, 106575, 113726, 109121)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 3-frame window freezes the video after more than 3 lost frames. Counter width, wrap, start value and the rollover and initialization policies are not defined. 106575 overlaps 113727.</t>
   </si>
   <si>
     <t xml:space="preserve">Concept / system, plus SWE for the check order</t>
@@ -1874,7 +2778,7 @@
     <t xml:space="preserve">6. Authentication is a static signature</t>
   </si>
   <si>
-    <t xml:space="preserve">107642, 107641, 103040</t>
+    <t xml:space="preserve">107642, 107641, 103040 (TCR 106565, 106563, 106577)</t>
   </si>
   <si>
     <t xml:space="preserve">A copied authentication record passes the signature check. Only the CMAC from frame 18 proves the private key. The signed message and the KID meaning must be defined.</t>
@@ -1883,10 +2787,10 @@
     <t xml:space="preserve">7. Layouts and crypto parameters</t>
   </si>
   <si>
-    <t xml:space="preserve">107641, 113705, 103055, 103033, 119707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSS salt and MGF, OAEP label, footer layout, CMAC input bytes and command field order are not stated. They come from the Samsung note (not in the repo).</t>
+    <t xml:space="preserve">107641, 113705, 103055, 103033, 119707 (TCR 106563, 106572, 106578, 106580, 106583, 106570)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSS salt and MGF, OAEP label, footer layout, message layout, CMAC input bytes and command field order are not stated. They come from the Samsung note (not in the repo).</t>
   </si>
   <si>
     <t xml:space="preserve">SWE scope</t>
@@ -1895,16 +2799,19 @@
     <t xml:space="preserve">8. Protected commands unclear</t>
   </si>
   <si>
-    <t xml:space="preserve">The Volvo spec has no protected command channel, and the imager may not check the tag or counter. Command list and format are missing.</t>
+    <t xml:space="preserve">119714, 113701, 119707, 113702 (TCR 109119, 108740, 106570, 109121)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Volvo spec has no protected command channel, and the imager may not check the tag or counter. Command list and format are missing. "Control" and "protected" are used for the same thing.</t>
   </si>
   <si>
     <t xml:space="preserve">9. Key handling</t>
   </si>
   <si>
-    <t xml:space="preserve">103063, 103057, 103042, 113706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTP zone and "no modification" are missing. New key per session is only in the verification text. The SSK in DRAM is readable through authorised debug. TRNG conformity is a Review item.</t>
+    <t xml:space="preserve">103063, 103057, 103042, 113706 (TCR 106562, 106568, 106560, 106571)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTP location and "no modification" are missing. New key per session and no TRNG fallback are only in the criteria. The SSK in DRAM is readable through authorised debug. TRNG conformity is a Review item.</t>
   </si>
   <si>
     <t xml:space="preserve">Concept / system, plus SWE for reseed and erase</t>
@@ -1916,7 +2823,7 @@
     <t xml:space="preserve">119709/119710, 103057/103042/103036, 113701/119707/113702</t>
   </si>
   <si>
-    <t xml:space="preserve">Several requirements are halves of one function, and technical requirements often copy the concept text without adding the how.</t>
+    <t xml:space="preserve">Several requirements are halves of one function. 15 of 30 TCRs have exactly the same text as their concept requirement and add the "how" only in the criteria.</t>
   </si>
   <si>
     <t xml:space="preserve">11. Traceability gaps</t>
@@ -1925,10 +2832,37 @@
     <t xml:space="preserve">119709, 107641, 113703, all</t>
   </si>
   <si>
-    <t xml:space="preserve">Upstream link MVC-106231 is too generic, MVC-106563 has no link to 107641, and the recovery rule and the 17-frame rule are in no requirement. SRS links are missing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12. Test needs</t>
+    <t xml:space="preserve">Upstream links are generic (26 TCRs link to the same four items). MVC-106563 has no link to 107641. The recovery rule and the 17-frame rule are in no requirement. SRS links are missing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. TCR criteria use undefined policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCR 106561, 106575, 106576, 106578, 106580, 106583, 109121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The criteria refer to rules that no document defines: retry behaviour, counter-validation, configuration validation, message layout, interface specification, input encoding, rollover and initialization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Row-information rules are under the wrong requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103055 (TCR 106574, 106576, 108741)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row start, interval and range rules sit under the encryption requirement. Give row selection its own concept requirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. TCR inconsistencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCR 106562, 106569, 106563, 109119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106562 criteria mention Secure Boot, 106569 fixes three attempts, 106563 has a typo and a missing step, 109119 uses another subject.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. Test needs</t>
   </si>
   <si>
     <t xml:space="preserve">Tests need a SOW1 simulator, a test root key, the Samsung documents, and a list of protected commands and interfaces.</t>
@@ -1949,12 +2883,18 @@
     <t xml:space="preserve">SRS reference</t>
   </si>
   <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSS salt length, MGF and public exponent</t>
   </si>
   <si>
     <t xml:space="preserve">SRS 108120, 108135</t>
   </si>
   <si>
+    <t xml:space="preserve">Concept</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reseed rule for the CSPRNG</t>
   </si>
   <si>
@@ -2001,6 +2941,30 @@
   </si>
   <si>
     <t xml:space="preserve">SRS 108160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRS 108120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reseed rule and "approved seeding mechanism"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter update only after authentication (in criteria, not in text)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real configured sizes, no integer overflow or truncation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRS 23.2.4.2 (row selection)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full 128-bit tag, no truncation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No command sent as protected if CMAC fails</t>
   </si>
 </sst>
 </file>
@@ -2010,7 +2974,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2056,6 +3020,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
@@ -2084,7 +3056,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2095,6 +3067,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
         <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -2147,8 +3125,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2164,23 +3146,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2193,11 +3179,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F3864"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E2F3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2243,7 +3237,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -2469,1071 +3463,2293 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="L2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="L3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="L4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="L5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="L6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="L7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="L8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="L9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="L10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="L11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="L12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="L13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="L14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="L15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+      <c r="L16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="L17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+      <c r="L18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
+      <c r="L19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
+      <c r="L20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K21" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
+      <c r="L21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
+      <c r="L22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+      <c r="L23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+      <c r="L24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="K25" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
+      <c r="L25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="K26" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
+      <c r="L26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+    </row>
+    <row r="38" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" customFormat="false" ht="187.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N26"/>
-  <dataValidations count="1">
+  <autoFilter ref="A1:N57"/>
+  <dataValidations count="2">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L26" type="list">
+      <formula1>"OPEN,AGREED,CHANGE REQUESTED,REJECTED,CLARIFY WITH EXTERNAL"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L28:L57" type="list">
       <formula1>"OPEN,AGREED,CHANGE REQUESTED,REJECTED,CLARIFY WITH EXTERNAL"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3557,1400 +5773,1400 @@
   <dimension ref="A1:S26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="H1" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>261</v>
+      <c r="S1" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
+      <c r="H2" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="H3" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
+      <c r="H4" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
+      <c r="H5" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="H6" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
+      <c r="H7" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="D8" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
+      <c r="H8" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
+      <c r="H9" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
+      <c r="H10" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="D11" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
+      <c r="H11" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
+      <c r="H12" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="D13" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
+      <c r="H13" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+      <c r="H14" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+      <c r="H15" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="D16" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
+      <c r="H16" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
+      <c r="H17" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="D18" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
+      <c r="H18" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="D19" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
+      <c r="H19" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="D20" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
+      <c r="H20" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="D21" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
+      <c r="H21" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="D22" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
+      <c r="H22" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="D23" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
+      <c r="H23" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="D24" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
+      <c r="H24" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="D25" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
+      <c r="H25" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="D26" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
+      <c r="H26" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S26"/>
@@ -4979,194 +7195,194 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="C1" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="2"/>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5190,425 +7406,691 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="80"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="B5" s="7" t="n">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <f aca="false">COUNTA(Review!B2:B26)</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="B6" s="7" t="n">
+      <c r="C5" s="9" t="n">
+        <f aca="false">COUNTA(Review!B28:B57)</f>
+        <v>30</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <f aca="false">B5+C5</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <f aca="false">COUNTIF(Review!E2:E26,"&lt;&gt;-")</f>
         <v>23</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="B7" s="7" t="n">
+      <c r="C6" s="9" t="n">
+        <f aca="false">COUNTIF(Review!E28:E57,"&lt;&gt;-")</f>
+        <v>28</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <f aca="false">B6+C6</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>811</v>
+      </c>
+      <c r="B7" s="9" t="n">
         <f aca="false">COUNTIF(Review!F2:F26,"&lt;&gt;-")</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="B8" s="7" t="n">
+      <c r="C7" s="9" t="n">
+        <f aca="false">COUNTIF(Review!F28:F57,"&lt;&gt;-")</f>
+        <v>30</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <f aca="false">B7+C7</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="B8" s="9" t="n">
         <f aca="false">COUNTIF(Review!G2:G26,"&lt;&gt;-")</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="B9" s="7" t="n">
+      <c r="C8" s="9" t="n">
+        <f aca="false">COUNTIF(Review!G28:G57,"&lt;&gt;-")</f>
+        <v>30</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <f aca="false">B8+C8</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="B9" s="9" t="n">
         <f aca="false">COUNTIF(Review!H2:H26,"&lt;&gt;-")</f>
         <v>23</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="B10" s="7" t="n">
+      <c r="C9" s="9" t="n">
+        <f aca="false">COUNTIF(Review!H28:H57,"&lt;&gt;-")</f>
+        <v>28</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <f aca="false">B9+C9</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF(Review!I2:I26,"&lt;&gt;-")</f>
         <v>19</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="B11" s="7" t="n">
+      <c r="C10" s="9" t="n">
+        <f aca="false">COUNTIF(Review!I28:I57,"&lt;&gt;-")</f>
+        <v>29</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <f aca="false">B10+C10</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="B11" s="9" t="n">
         <f aca="false">COUNTIF(Review!J2:J26,"&lt;&gt;-")</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="B12" s="7" t="n">
+      <c r="C11" s="9" t="n">
+        <f aca="false">COUNTIF(Review!J28:J57,"&lt;&gt;-")</f>
+        <v>30</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <f aca="false">B11+C11</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="B12" s="9" t="n">
         <f aca="false">COUNTIF(Review!E2:J26,"*SWE:*")</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="B13" s="7" t="n">
+      <c r="C12" s="9" t="n">
+        <f aca="false">COUNTIF(Review!E28:J57,"*SWE:*")</f>
+        <v>9</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <f aca="false">B12+C12</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="B13" s="9" t="n">
         <f aca="false">COUNTIF(Review!L2:L26,"OPEN")</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>536</v>
+      <c r="C13" s="9" t="n">
+        <f aca="false">COUNTIF(Review!L28:L57,"OPEN")</f>
+        <v>30</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <f aca="false">B13+C13</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>540</v>
+      <c r="A17" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>540</v>
+      <c r="A18" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>540</v>
+      <c r="A19" s="9" t="s">
+        <v>830</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>540</v>
+      <c r="A20" s="9" t="s">
+        <v>833</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>835</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>552</v>
+      <c r="A21" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>839</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>540</v>
+      <c r="A22" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>559</v>
+      <c r="A23" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>540</v>
+      <c r="A24" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>849</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>565</v>
+      <c r="A25" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>540</v>
+      <c r="A26" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>540</v>
+      <c r="A27" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
+      <c r="A28" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>863</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>865</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>801</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="D32" s="7"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="B35" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>581</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="D33" s="7"/>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
+      <c r="B36" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="D34" s="7"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
+      <c r="B37" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="D35" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
+      <c r="B38" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="D36" s="7"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
+      <c r="B39" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="D37" s="7"/>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="B40" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="D38" s="7"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
+      <c r="B41" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="D39" s="7"/>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="B42" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>596</v>
-      </c>
-      <c r="D40" s="7"/>
+      <c r="B43" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>897</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
